--- a/backend/templates/UC-18gsm-250P-ABQR.xlsx
+++ b/backend/templates/UC-18gsm-250P-ABQR.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4E08BB-8CFC-46F9-A491-90537B509400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D54676-1AE9-40A9-A7F7-0AFE915A2CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page1" sheetId="6" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -472,14 +475,6 @@
     <t>U-</t>
   </si>
   <si>
-    <t>Colour B
-L-(-12.50) T-(-8.50) U-(-4.50)</t>
-  </si>
-  <si>
-    <t>Colour L
-L-52.00 T-58.00 U-64.00</t>
-  </si>
-  <si>
     <t>Colour A
 L-49.00 T-54.00 U-59.00</t>
   </si>
@@ -514,6 +509,14 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>Colour L
+L-54.00 T-59.00 U-63.00</t>
+  </si>
+  <si>
+    <t>Colour B
+L-(-11.50) T-(-8.50) U-(-5.50)</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1864,6 +1867,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2408,7 +2414,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="18">
     <dxf>
       <font>
         <strike/>
@@ -2449,44 +2455,6 @@
         <strike/>
         <color rgb="FFFF0000"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2607,45 +2575,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3049,35 +2978,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="152" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
       <c r="K1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="152" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="151"/>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="151"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
       <c r="K2" s="16" t="s">
         <v>29</v>
       </c>
@@ -3098,12 +3027,12 @@
       <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:13" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="153"/>
-      <c r="C4" s="160"/>
-      <c r="D4" s="161"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="161"/>
+      <c r="D4" s="162"/>
       <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3115,19 +3044,19 @@
       <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167"/>
-      <c r="K4" s="168"/>
+      <c r="J4" s="168"/>
+      <c r="K4" s="169"/>
       <c r="M4" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="15" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="159"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="163"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="164"/>
       <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
@@ -3139,64 +3068,64 @@
       <c r="I5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="169"/>
-      <c r="K5" s="170"/>
+      <c r="J5" s="170"/>
+      <c r="K5" s="171"/>
     </row>
     <row r="6" spans="1:13" s="15" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="133" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="134"/>
-      <c r="C6" s="135"/>
+      <c r="A6" s="134" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="165"/>
+        <v>140</v>
+      </c>
+      <c r="G6" s="157"/>
+      <c r="H6" s="158"/>
+      <c r="I6" s="157"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="166"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="136" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="137"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137" t="s">
+      <c r="A7" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="137" t="s">
+      <c r="F7" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="154" t="s">
+      <c r="G7" s="155" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="154" t="s">
+      <c r="H7" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="I7" s="137" t="s">
+      <c r="I7" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="137"/>
-      <c r="K7" s="166"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="167"/>
     </row>
     <row r="8" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138"/>
-      <c r="B8" s="139"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139" t="s">
+      <c r="A8" s="139"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="139"/>
-      <c r="G8" s="155"/>
-      <c r="H8" s="155"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="156"/>
+      <c r="H8" s="156"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3598,11 +3527,11 @@
       <c r="K38" s="72"/>
     </row>
     <row r="39" spans="1:14" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="146" t="s">
+      <c r="A39" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="147"/>
-      <c r="C39" s="148"/>
+      <c r="B39" s="148"/>
+      <c r="C39" s="149"/>
       <c r="D39" s="30" t="e">
         <f t="shared" ref="D39:K39" si="0">AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3637,11 +3566,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="143" t="s">
+      <c r="A40" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="144"/>
-      <c r="C40" s="145"/>
+      <c r="B40" s="145"/>
+      <c r="C40" s="146"/>
       <c r="D40" s="33">
         <f t="shared" ref="D40:K40" si="1">MIN(D9:D38)</f>
         <v>0</v>
@@ -3676,11 +3605,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="140" t="s">
+      <c r="A41" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="141"/>
-      <c r="C41" s="142"/>
+      <c r="B41" s="142"/>
+      <c r="C41" s="143"/>
       <c r="D41" s="79">
         <f t="shared" ref="D41:K41" si="2">MAX(D9:D38)</f>
         <v>0</v>
@@ -3721,8 +3650,8 @@
       <c r="A42" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="150"/>
-      <c r="C42" s="150"/>
+      <c r="B42" s="151"/>
+      <c r="C42" s="151"/>
       <c r="D42" s="38" t="s">
         <v>22</v>
       </c>
@@ -3739,8 +3668,8 @@
     </row>
     <row r="43" spans="1:14" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="43"/>
-      <c r="B43" s="149"/>
-      <c r="C43" s="149"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="150"/>
       <c r="D43" s="38"/>
       <c r="F43" s="39"/>
       <c r="G43" s="40"/>
@@ -3749,15 +3678,15 @@
       <c r="J43" s="17"/>
     </row>
     <row r="44" spans="1:14" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="132" t="s">
+      <c r="A44" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="132"/>
-      <c r="C44" s="132"/>
+      <c r="B44" s="133"/>
+      <c r="C44" s="133"/>
       <c r="D44" s="38"/>
       <c r="E44" s="38"/>
       <c r="F44" s="40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G44" s="39">
         <v>461303600</v>
@@ -3765,11 +3694,11 @@
       <c r="H44" s="38"/>
     </row>
     <row r="45" spans="1:14" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="132" t="s">
-        <v>133</v>
-      </c>
-      <c r="B45" s="132"/>
-      <c r="C45" s="132"/>
+      <c r="A45" s="133" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="133"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
       <c r="F45" s="38"/>
@@ -3825,64 +3754,48 @@
     <mergeCell ref="B42:C42"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:D41">
-    <cfRule type="cellIs" dxfId="24" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="notBetween">
+      <formula>17</formula>
       <formula>20</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="19" operator="lessThan">
-      <formula>17</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E41">
-    <cfRule type="cellIs" dxfId="22" priority="16" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="notBetween">
+      <formula>18</formula>
       <formula>28</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="17" operator="lessThan">
-      <formula>18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F41">
-    <cfRule type="cellIs" dxfId="20" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="notBetween">
+      <formula>360</formula>
       <formula>400</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="14" operator="lessThan">
-      <formula>360</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G41">
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="notBetween">
+      <formula>0.3</formula>
       <formula>0.6</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="12" operator="lessThan">
-      <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H38">
-    <cfRule type="cellIs" dxfId="16" priority="1" stopIfTrue="1" operator="notBetween">
-      <formula>0.6</formula>
-      <formula>1.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="cellIs" priority="4" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="1" stopIfTrue="1" operator="notBetween">
       <formula>0.6</formula>
       <formula>1.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I41">
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="notBetween">
+      <formula>900</formula>
       <formula>1200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="lessThan">
-      <formula>900</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J41">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
       <formula>350</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K41">
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3905,35 +3818,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="152" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
       <c r="K1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="152" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="151"/>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="151"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
       <c r="K2" s="16" t="s">
         <v>29</v>
       </c>
@@ -3954,18 +3867,18 @@
       <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="153">
+      <c r="B4" s="154">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="208">
+      <c r="C4" s="209">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="209"/>
+      <c r="D4" s="210"/>
       <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3983,25 +3896,25 @@
       <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="200">
+      <c r="J4" s="201">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="201"/>
+      <c r="K4" s="202"/>
     </row>
     <row r="5" spans="1:11" s="15" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="159">
+      <c r="B5" s="160">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="162">
+      <c r="C5" s="163">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="163"/>
+      <c r="D5" s="164"/>
       <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
@@ -4019,104 +3932,104 @@
       <c r="I5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="202">
+      <c r="J5" s="203">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="203"/>
+      <c r="K5" s="204"/>
     </row>
     <row r="6" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="212" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="213"/>
-      <c r="C6" s="214"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="195"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="193"/>
-      <c r="H6" s="194"/>
-      <c r="I6" s="191"/>
-      <c r="J6" s="192"/>
+      <c r="A6" s="213" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="214"/>
+      <c r="C6" s="215"/>
+      <c r="D6" s="211"/>
+      <c r="E6" s="196"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="194"/>
+      <c r="H6" s="195"/>
+      <c r="I6" s="192"/>
+      <c r="J6" s="193"/>
       <c r="K6" s="20"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="210" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="195"/>
-      <c r="C7" s="195"/>
-      <c r="D7" s="217" t="s">
+      <c r="A7" s="211" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="196"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="195"/>
-      <c r="F7" s="209"/>
-      <c r="G7" s="193" t="s">
+      <c r="E7" s="196"/>
+      <c r="F7" s="210"/>
+      <c r="G7" s="194" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="195"/>
-      <c r="I7" s="193" t="s">
-        <v>135</v>
-      </c>
-      <c r="J7" s="194"/>
-      <c r="K7" s="205" t="s">
+      <c r="H7" s="196"/>
+      <c r="I7" s="194" t="s">
+        <v>133</v>
+      </c>
+      <c r="J7" s="195"/>
+      <c r="K7" s="206" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="211"/>
-      <c r="B8" s="197"/>
-      <c r="C8" s="197"/>
-      <c r="D8" s="211" t="s">
+      <c r="A8" s="212"/>
+      <c r="B8" s="198"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="212" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="223" t="s">
+      <c r="E8" s="224" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="204" t="s">
+      <c r="F8" s="205" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="196"/>
-      <c r="H8" s="197"/>
-      <c r="I8" s="196" t="s">
-        <v>134</v>
-      </c>
-      <c r="J8" s="204"/>
-      <c r="K8" s="206"/>
+      <c r="G8" s="197"/>
+      <c r="H8" s="198"/>
+      <c r="I8" s="197" t="s">
+        <v>132</v>
+      </c>
+      <c r="J8" s="205"/>
+      <c r="K8" s="207"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="211"/>
-      <c r="B9" s="197"/>
-      <c r="C9" s="197"/>
-      <c r="D9" s="211"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="197"/>
+      <c r="A9" s="212"/>
+      <c r="B9" s="198"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="212"/>
+      <c r="E9" s="155"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="197"/>
+      <c r="H9" s="198"/>
       <c r="I9" s="47" t="s">
         <v>128</v>
       </c>
       <c r="J9" s="48">
         <v>250</v>
       </c>
-      <c r="K9" s="206"/>
+      <c r="K9" s="207"/>
     </row>
     <row r="10" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="211"/>
-      <c r="B10" s="197"/>
-      <c r="C10" s="197"/>
-      <c r="D10" s="222"/>
-      <c r="E10" s="155"/>
-      <c r="F10" s="224"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="199"/>
+      <c r="A10" s="212"/>
+      <c r="B10" s="198"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="156"/>
+      <c r="F10" s="225"/>
+      <c r="G10" s="199"/>
+      <c r="H10" s="200"/>
       <c r="I10" s="49" t="s">
         <v>129</v>
       </c>
       <c r="J10" s="50">
         <v>253</v>
       </c>
-      <c r="K10" s="207"/>
+      <c r="K10" s="208"/>
     </row>
     <row r="11" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="86">
@@ -4134,10 +4047,10 @@
       <c r="D11" s="51"/>
       <c r="E11" s="52"/>
       <c r="F11" s="52"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="187"/>
-      <c r="J11" s="188"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="188"/>
+      <c r="J11" s="189"/>
       <c r="K11" s="53"/>
     </row>
     <row r="12" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4156,10 +4069,10 @@
       <c r="D12" s="54"/>
       <c r="E12" s="55"/>
       <c r="F12" s="55"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="173"/>
-      <c r="J12" s="174"/>
+      <c r="G12" s="177"/>
+      <c r="H12" s="177"/>
+      <c r="I12" s="174"/>
+      <c r="J12" s="175"/>
       <c r="K12" s="56"/>
     </row>
     <row r="13" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4178,10 +4091,10 @@
       <c r="D13" s="54"/>
       <c r="E13" s="55"/>
       <c r="F13" s="55"/>
-      <c r="G13" s="176"/>
-      <c r="H13" s="176"/>
-      <c r="I13" s="173"/>
-      <c r="J13" s="174"/>
+      <c r="G13" s="177"/>
+      <c r="H13" s="177"/>
+      <c r="I13" s="174"/>
+      <c r="J13" s="175"/>
       <c r="K13" s="56"/>
     </row>
     <row r="14" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4200,10 +4113,10 @@
       <c r="D14" s="54"/>
       <c r="E14" s="55"/>
       <c r="F14" s="55"/>
-      <c r="G14" s="176"/>
-      <c r="H14" s="176"/>
-      <c r="I14" s="173"/>
-      <c r="J14" s="174"/>
+      <c r="G14" s="177"/>
+      <c r="H14" s="177"/>
+      <c r="I14" s="174"/>
+      <c r="J14" s="175"/>
       <c r="K14" s="56"/>
     </row>
     <row r="15" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4222,10 +4135,10 @@
       <c r="D15" s="54"/>
       <c r="E15" s="55"/>
       <c r="F15" s="55"/>
-      <c r="G15" s="176"/>
-      <c r="H15" s="176"/>
-      <c r="I15" s="173"/>
-      <c r="J15" s="174"/>
+      <c r="G15" s="177"/>
+      <c r="H15" s="177"/>
+      <c r="I15" s="174"/>
+      <c r="J15" s="175"/>
       <c r="K15" s="56"/>
     </row>
     <row r="16" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4244,10 +4157,10 @@
       <c r="D16" s="51"/>
       <c r="E16" s="52"/>
       <c r="F16" s="52"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="175"/>
-      <c r="I16" s="173"/>
-      <c r="J16" s="174"/>
+      <c r="G16" s="176"/>
+      <c r="H16" s="176"/>
+      <c r="I16" s="174"/>
+      <c r="J16" s="175"/>
       <c r="K16" s="53"/>
     </row>
     <row r="17" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4266,10 +4179,10 @@
       <c r="D17" s="54"/>
       <c r="E17" s="55"/>
       <c r="F17" s="55"/>
-      <c r="G17" s="176"/>
-      <c r="H17" s="176"/>
-      <c r="I17" s="173"/>
-      <c r="J17" s="174"/>
+      <c r="G17" s="177"/>
+      <c r="H17" s="177"/>
+      <c r="I17" s="174"/>
+      <c r="J17" s="175"/>
       <c r="K17" s="56"/>
     </row>
     <row r="18" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4288,10 +4201,10 @@
       <c r="D18" s="54"/>
       <c r="E18" s="55"/>
       <c r="F18" s="55"/>
-      <c r="G18" s="176"/>
-      <c r="H18" s="176"/>
-      <c r="I18" s="173"/>
-      <c r="J18" s="174"/>
+      <c r="G18" s="177"/>
+      <c r="H18" s="177"/>
+      <c r="I18" s="174"/>
+      <c r="J18" s="175"/>
       <c r="K18" s="56"/>
     </row>
     <row r="19" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4310,10 +4223,10 @@
       <c r="D19" s="54"/>
       <c r="E19" s="55"/>
       <c r="F19" s="55"/>
-      <c r="G19" s="176"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="173"/>
-      <c r="J19" s="174"/>
+      <c r="G19" s="177"/>
+      <c r="H19" s="177"/>
+      <c r="I19" s="174"/>
+      <c r="J19" s="175"/>
       <c r="K19" s="56"/>
     </row>
     <row r="20" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4332,10 +4245,10 @@
       <c r="D20" s="54"/>
       <c r="E20" s="55"/>
       <c r="F20" s="55"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="172"/>
-      <c r="I20" s="173"/>
-      <c r="J20" s="174"/>
+      <c r="G20" s="172"/>
+      <c r="H20" s="173"/>
+      <c r="I20" s="174"/>
+      <c r="J20" s="175"/>
       <c r="K20" s="56"/>
     </row>
     <row r="21" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4354,10 +4267,10 @@
       <c r="D21" s="54"/>
       <c r="E21" s="55"/>
       <c r="F21" s="55"/>
-      <c r="G21" s="171"/>
-      <c r="H21" s="172"/>
-      <c r="I21" s="173"/>
-      <c r="J21" s="174"/>
+      <c r="G21" s="172"/>
+      <c r="H21" s="173"/>
+      <c r="I21" s="174"/>
+      <c r="J21" s="175"/>
       <c r="K21" s="56"/>
     </row>
     <row r="22" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4376,10 +4289,10 @@
       <c r="D22" s="54"/>
       <c r="E22" s="55"/>
       <c r="F22" s="55"/>
-      <c r="G22" s="171"/>
-      <c r="H22" s="172"/>
-      <c r="I22" s="173"/>
-      <c r="J22" s="174"/>
+      <c r="G22" s="172"/>
+      <c r="H22" s="173"/>
+      <c r="I22" s="174"/>
+      <c r="J22" s="175"/>
       <c r="K22" s="56"/>
     </row>
     <row r="23" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4398,10 +4311,10 @@
       <c r="D23" s="54"/>
       <c r="E23" s="55"/>
       <c r="F23" s="55"/>
-      <c r="G23" s="171"/>
-      <c r="H23" s="172"/>
-      <c r="I23" s="173"/>
-      <c r="J23" s="174"/>
+      <c r="G23" s="172"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="174"/>
+      <c r="J23" s="175"/>
       <c r="K23" s="56"/>
     </row>
     <row r="24" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4420,10 +4333,10 @@
       <c r="D24" s="54"/>
       <c r="E24" s="55"/>
       <c r="F24" s="55"/>
-      <c r="G24" s="171"/>
-      <c r="H24" s="172"/>
-      <c r="I24" s="173"/>
-      <c r="J24" s="174"/>
+      <c r="G24" s="172"/>
+      <c r="H24" s="173"/>
+      <c r="I24" s="174"/>
+      <c r="J24" s="175"/>
       <c r="K24" s="56"/>
     </row>
     <row r="25" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4442,10 +4355,10 @@
       <c r="D25" s="54"/>
       <c r="E25" s="55"/>
       <c r="F25" s="55"/>
-      <c r="G25" s="171"/>
-      <c r="H25" s="172"/>
-      <c r="I25" s="173"/>
-      <c r="J25" s="174"/>
+      <c r="G25" s="172"/>
+      <c r="H25" s="173"/>
+      <c r="I25" s="174"/>
+      <c r="J25" s="175"/>
       <c r="K25" s="56"/>
     </row>
     <row r="26" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4464,10 +4377,10 @@
       <c r="D26" s="54"/>
       <c r="E26" s="55"/>
       <c r="F26" s="55"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="172"/>
-      <c r="I26" s="173"/>
-      <c r="J26" s="174"/>
+      <c r="G26" s="172"/>
+      <c r="H26" s="173"/>
+      <c r="I26" s="174"/>
+      <c r="J26" s="175"/>
       <c r="K26" s="56"/>
     </row>
     <row r="27" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4486,10 +4399,10 @@
       <c r="D27" s="54"/>
       <c r="E27" s="55"/>
       <c r="F27" s="55"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="172"/>
-      <c r="I27" s="173"/>
-      <c r="J27" s="174"/>
+      <c r="G27" s="172"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="175"/>
       <c r="K27" s="56"/>
     </row>
     <row r="28" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4508,10 +4421,10 @@
       <c r="D28" s="54"/>
       <c r="E28" s="55"/>
       <c r="F28" s="55"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="172"/>
-      <c r="I28" s="173"/>
-      <c r="J28" s="174"/>
+      <c r="G28" s="172"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="175"/>
       <c r="K28" s="56"/>
     </row>
     <row r="29" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4530,10 +4443,10 @@
       <c r="D29" s="54"/>
       <c r="E29" s="55"/>
       <c r="F29" s="55"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="172"/>
-      <c r="I29" s="173"/>
-      <c r="J29" s="174"/>
+      <c r="G29" s="172"/>
+      <c r="H29" s="173"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="175"/>
       <c r="K29" s="56"/>
     </row>
     <row r="30" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4552,10 +4465,10 @@
       <c r="D30" s="54"/>
       <c r="E30" s="55"/>
       <c r="F30" s="55"/>
-      <c r="G30" s="171"/>
-      <c r="H30" s="172"/>
-      <c r="I30" s="173"/>
-      <c r="J30" s="174"/>
+      <c r="G30" s="172"/>
+      <c r="H30" s="173"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="175"/>
       <c r="K30" s="56"/>
     </row>
     <row r="31" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4574,10 +4487,10 @@
       <c r="D31" s="54"/>
       <c r="E31" s="55"/>
       <c r="F31" s="55"/>
-      <c r="G31" s="171"/>
-      <c r="H31" s="172"/>
-      <c r="I31" s="173"/>
-      <c r="J31" s="174"/>
+      <c r="G31" s="172"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="174"/>
+      <c r="J31" s="175"/>
       <c r="K31" s="56"/>
     </row>
     <row r="32" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4596,10 +4509,10 @@
       <c r="D32" s="54"/>
       <c r="E32" s="55"/>
       <c r="F32" s="55"/>
-      <c r="G32" s="171"/>
-      <c r="H32" s="172"/>
-      <c r="I32" s="173"/>
-      <c r="J32" s="174"/>
+      <c r="G32" s="172"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="174"/>
+      <c r="J32" s="175"/>
       <c r="K32" s="56"/>
     </row>
     <row r="33" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4618,10 +4531,10 @@
       <c r="D33" s="54"/>
       <c r="E33" s="55"/>
       <c r="F33" s="55"/>
-      <c r="G33" s="171"/>
-      <c r="H33" s="172"/>
-      <c r="I33" s="173"/>
-      <c r="J33" s="174"/>
+      <c r="G33" s="172"/>
+      <c r="H33" s="173"/>
+      <c r="I33" s="174"/>
+      <c r="J33" s="175"/>
       <c r="K33" s="56"/>
     </row>
     <row r="34" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4640,10 +4553,10 @@
       <c r="D34" s="54"/>
       <c r="E34" s="55"/>
       <c r="F34" s="55"/>
-      <c r="G34" s="171"/>
-      <c r="H34" s="172"/>
-      <c r="I34" s="173"/>
-      <c r="J34" s="174"/>
+      <c r="G34" s="172"/>
+      <c r="H34" s="173"/>
+      <c r="I34" s="174"/>
+      <c r="J34" s="175"/>
       <c r="K34" s="56"/>
     </row>
     <row r="35" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4662,10 +4575,10 @@
       <c r="D35" s="54"/>
       <c r="E35" s="55"/>
       <c r="F35" s="55"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="172"/>
-      <c r="I35" s="173"/>
-      <c r="J35" s="174"/>
+      <c r="G35" s="172"/>
+      <c r="H35" s="173"/>
+      <c r="I35" s="174"/>
+      <c r="J35" s="175"/>
       <c r="K35" s="56"/>
     </row>
     <row r="36" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4684,10 +4597,10 @@
       <c r="D36" s="54"/>
       <c r="E36" s="55"/>
       <c r="F36" s="55"/>
-      <c r="G36" s="171"/>
-      <c r="H36" s="172"/>
-      <c r="I36" s="173"/>
-      <c r="J36" s="174"/>
+      <c r="G36" s="172"/>
+      <c r="H36" s="173"/>
+      <c r="I36" s="174"/>
+      <c r="J36" s="175"/>
       <c r="K36" s="56"/>
     </row>
     <row r="37" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4706,10 +4619,10 @@
       <c r="D37" s="54"/>
       <c r="E37" s="55"/>
       <c r="F37" s="55"/>
-      <c r="G37" s="171"/>
-      <c r="H37" s="172"/>
-      <c r="I37" s="173"/>
-      <c r="J37" s="174"/>
+      <c r="G37" s="172"/>
+      <c r="H37" s="173"/>
+      <c r="I37" s="174"/>
+      <c r="J37" s="175"/>
       <c r="K37" s="56"/>
     </row>
     <row r="38" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4728,10 +4641,10 @@
       <c r="D38" s="54"/>
       <c r="E38" s="55"/>
       <c r="F38" s="55"/>
-      <c r="G38" s="171"/>
-      <c r="H38" s="172"/>
-      <c r="I38" s="173"/>
-      <c r="J38" s="174"/>
+      <c r="G38" s="172"/>
+      <c r="H38" s="173"/>
+      <c r="I38" s="174"/>
+      <c r="J38" s="175"/>
       <c r="K38" s="56"/>
     </row>
     <row r="39" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4750,10 +4663,10 @@
       <c r="D39" s="54"/>
       <c r="E39" s="55"/>
       <c r="F39" s="55"/>
-      <c r="G39" s="171"/>
-      <c r="H39" s="172"/>
-      <c r="I39" s="173"/>
-      <c r="J39" s="174"/>
+      <c r="G39" s="172"/>
+      <c r="H39" s="173"/>
+      <c r="I39" s="174"/>
+      <c r="J39" s="175"/>
       <c r="K39" s="56"/>
     </row>
     <row r="40" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4772,18 +4685,18 @@
       <c r="D40" s="54"/>
       <c r="E40" s="55"/>
       <c r="F40" s="55"/>
-      <c r="G40" s="176"/>
-      <c r="H40" s="176"/>
-      <c r="I40" s="173"/>
-      <c r="J40" s="174"/>
+      <c r="G40" s="177"/>
+      <c r="H40" s="177"/>
+      <c r="I40" s="174"/>
+      <c r="J40" s="175"/>
       <c r="K40" s="56"/>
     </row>
     <row r="41" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="218" t="s">
+      <c r="A41" s="219" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="219"/>
-      <c r="C41" s="219"/>
+      <c r="B41" s="220"/>
+      <c r="C41" s="220"/>
       <c r="D41" s="57" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -4796,27 +4709,27 @@
         <f>AVERAGE(F11:F40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="179" t="e">
+      <c r="G41" s="180" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="180"/>
-      <c r="I41" s="177" t="e">
+      <c r="H41" s="181"/>
+      <c r="I41" s="178" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="178"/>
+      <c r="J41" s="179"/>
       <c r="K41" s="59" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="220" t="s">
+      <c r="A42" s="221" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="221"/>
-      <c r="C42" s="221"/>
+      <c r="B42" s="222"/>
+      <c r="C42" s="222"/>
       <c r="D42" s="60">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -4829,27 +4742,27 @@
         <f>MIN(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="185">
+      <c r="G42" s="186">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="186"/>
-      <c r="I42" s="189">
+      <c r="H42" s="187"/>
+      <c r="I42" s="190">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="190"/>
+      <c r="J42" s="191"/>
       <c r="K42" s="62">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="215" t="s">
+      <c r="A43" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="216"/>
-      <c r="C43" s="216"/>
+      <c r="B43" s="217"/>
+      <c r="C43" s="217"/>
       <c r="D43" s="63">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4862,16 +4775,16 @@
         <f>MAX(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="183">
+      <c r="G43" s="184">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="184"/>
-      <c r="I43" s="181">
+      <c r="H43" s="185"/>
+      <c r="I43" s="182">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="182"/>
+      <c r="J43" s="183"/>
       <c r="K43" s="65">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -4881,8 +4794,8 @@
       <c r="A44" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="150"/>
-      <c r="C44" s="150"/>
+      <c r="B44" s="151"/>
+      <c r="C44" s="151"/>
       <c r="D44" s="38" t="s">
         <v>22</v>
       </c>
@@ -4899,8 +4812,8 @@
     </row>
     <row r="45" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="43"/>
-      <c r="B45" s="149"/>
-      <c r="C45" s="149"/>
+      <c r="B45" s="150"/>
+      <c r="C45" s="150"/>
       <c r="D45" s="38"/>
       <c r="F45" s="39"/>
       <c r="G45" s="40"/>
@@ -4909,15 +4822,15 @@
       <c r="J45" s="17"/>
     </row>
     <row r="46" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="132" t="s">
+      <c r="A46" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="132"/>
-      <c r="C46" s="132"/>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
       <c r="D46" s="38"/>
       <c r="E46" s="38"/>
       <c r="F46" s="40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G46" s="39">
         <f>Page1!G44</f>
@@ -4926,11 +4839,11 @@
       <c r="H46" s="38"/>
     </row>
     <row r="47" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="132" t="s">
-        <v>133</v>
-      </c>
-      <c r="B47" s="132"/>
-      <c r="C47" s="132"/>
+      <c r="A47" s="133" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="133"/>
+      <c r="C47" s="133"/>
       <c r="D47" s="38"/>
       <c r="E47" s="38"/>
       <c r="F47" s="38"/>
@@ -5082,37 +4995,37 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="13" operator="notBetween">
+      <formula>700</formula>
       <formula>1000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="lessThan">
-      <formula>700</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:E43">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="lessThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F43">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="11" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H19 G20:G39 G40:H43">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="notBetween">
+      <formula>50</formula>
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="lessThan">
-      <formula>50</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:J43">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="notBetween">
+      <formula>250</formula>
+      <formula>253</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K43">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="notBetween">
+      <formula>410</formula>
       <formula>450</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="lessThan">
-      <formula>410</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5134,35 +5047,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="152" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
       <c r="K1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="152" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="151"/>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="151"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
       <c r="K2" s="16" t="s">
         <v>29</v>
       </c>
@@ -5183,15 +5096,15 @@
       <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="153"/>
-      <c r="C4" s="208">
+      <c r="B4" s="154"/>
+      <c r="C4" s="209">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="209"/>
+      <c r="D4" s="210"/>
       <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
@@ -5209,22 +5122,22 @@
       <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="200">
+      <c r="J4" s="201">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="201"/>
+      <c r="K4" s="202"/>
     </row>
     <row r="5" spans="1:11" s="15" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="159"/>
-      <c r="C5" s="162">
+      <c r="B5" s="160"/>
+      <c r="C5" s="163">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="163"/>
+      <c r="D5" s="164"/>
       <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
@@ -5242,79 +5155,79 @@
       <c r="I5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="202">
+      <c r="J5" s="203">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="203"/>
+      <c r="K5" s="204"/>
     </row>
     <row r="6" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="225" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="226"/>
-      <c r="C6" s="227"/>
-      <c r="D6" s="228"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="157"/>
+      <c r="A6" s="226" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="227"/>
+      <c r="C6" s="228"/>
+      <c r="D6" s="229"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="158"/>
       <c r="H6" s="19"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="195"/>
-      <c r="K6" s="205"/>
+      <c r="I6" s="211"/>
+      <c r="J6" s="196"/>
+      <c r="K6" s="206"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="210" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="195"/>
-      <c r="C7" s="195"/>
-      <c r="D7" s="217" t="s">
+      <c r="A7" s="211" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="196"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="218" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="234"/>
-      <c r="F7" s="234"/>
-      <c r="G7" s="209"/>
-      <c r="H7" s="229" t="s">
+      <c r="E7" s="235"/>
+      <c r="F7" s="235"/>
+      <c r="G7" s="210"/>
+      <c r="H7" s="230" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="211"/>
-      <c r="J7" s="197"/>
-      <c r="K7" s="206"/>
+      <c r="I7" s="212"/>
+      <c r="J7" s="198"/>
+      <c r="K7" s="207"/>
     </row>
     <row r="8" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="211"/>
-      <c r="B8" s="197"/>
-      <c r="C8" s="197"/>
-      <c r="D8" s="232" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="223" t="s">
-        <v>132</v>
-      </c>
-      <c r="F8" s="223" t="s">
+      <c r="A8" s="212"/>
+      <c r="B8" s="198"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="233" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" s="224" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="223" t="s">
+      <c r="F8" s="224" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="224" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="230"/>
-      <c r="I8" s="211"/>
-      <c r="J8" s="197"/>
-      <c r="K8" s="206"/>
+      <c r="H8" s="231"/>
+      <c r="I8" s="212"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="207"/>
     </row>
     <row r="9" spans="1:11" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="211"/>
-      <c r="B9" s="197"/>
-      <c r="C9" s="197"/>
-      <c r="D9" s="233"/>
-      <c r="E9" s="155"/>
-      <c r="F9" s="155"/>
-      <c r="G9" s="155"/>
-      <c r="H9" s="231"/>
-      <c r="I9" s="211"/>
-      <c r="J9" s="197"/>
-      <c r="K9" s="206"/>
+      <c r="A9" s="212"/>
+      <c r="B9" s="198"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="156"/>
+      <c r="F9" s="156"/>
+      <c r="G9" s="156"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="198"/>
+      <c r="K9" s="207"/>
     </row>
     <row r="10" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="86">
@@ -5334,9 +5247,9 @@
       <c r="F10" s="22"/>
       <c r="G10" s="23"/>
       <c r="H10" s="24"/>
-      <c r="I10" s="211"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="206"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="198"/>
+      <c r="K10" s="207"/>
     </row>
     <row r="11" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="89">
@@ -5356,9 +5269,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="27"/>
       <c r="H11" s="28"/>
-      <c r="I11" s="211"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="206"/>
+      <c r="I11" s="212"/>
+      <c r="J11" s="198"/>
+      <c r="K11" s="207"/>
     </row>
     <row r="12" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="89">
@@ -5378,9 +5291,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="27"/>
       <c r="H12" s="28"/>
-      <c r="I12" s="211"/>
-      <c r="J12" s="197"/>
-      <c r="K12" s="206"/>
+      <c r="I12" s="212"/>
+      <c r="J12" s="198"/>
+      <c r="K12" s="207"/>
     </row>
     <row r="13" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="89">
@@ -5400,9 +5313,9 @@
       <c r="F13" s="22"/>
       <c r="G13" s="23"/>
       <c r="H13" s="28"/>
-      <c r="I13" s="211"/>
-      <c r="J13" s="197"/>
-      <c r="K13" s="206"/>
+      <c r="I13" s="212"/>
+      <c r="J13" s="198"/>
+      <c r="K13" s="207"/>
     </row>
     <row r="14" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="89">
@@ -5422,9 +5335,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="27"/>
       <c r="H14" s="28"/>
-      <c r="I14" s="211"/>
-      <c r="J14" s="197"/>
-      <c r="K14" s="206"/>
+      <c r="I14" s="212"/>
+      <c r="J14" s="198"/>
+      <c r="K14" s="207"/>
     </row>
     <row r="15" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="89">
@@ -5444,9 +5357,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="27"/>
       <c r="H15" s="28"/>
-      <c r="I15" s="211"/>
-      <c r="J15" s="197"/>
-      <c r="K15" s="206"/>
+      <c r="I15" s="212"/>
+      <c r="J15" s="198"/>
+      <c r="K15" s="207"/>
     </row>
     <row r="16" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="89">
@@ -5466,9 +5379,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="27"/>
       <c r="H16" s="28"/>
-      <c r="I16" s="211"/>
-      <c r="J16" s="197"/>
-      <c r="K16" s="206"/>
+      <c r="I16" s="212"/>
+      <c r="J16" s="198"/>
+      <c r="K16" s="207"/>
     </row>
     <row r="17" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="89">
@@ -5488,9 +5401,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="27"/>
       <c r="H17" s="28"/>
-      <c r="I17" s="211"/>
-      <c r="J17" s="197"/>
-      <c r="K17" s="206"/>
+      <c r="I17" s="212"/>
+      <c r="J17" s="198"/>
+      <c r="K17" s="207"/>
     </row>
     <row r="18" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="89">
@@ -5510,9 +5423,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="27"/>
       <c r="H18" s="28"/>
-      <c r="I18" s="211"/>
-      <c r="J18" s="197"/>
-      <c r="K18" s="206"/>
+      <c r="I18" s="212"/>
+      <c r="J18" s="198"/>
+      <c r="K18" s="207"/>
     </row>
     <row r="19" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="89">
@@ -5532,9 +5445,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="27"/>
       <c r="H19" s="28"/>
-      <c r="I19" s="211"/>
-      <c r="J19" s="197"/>
-      <c r="K19" s="206"/>
+      <c r="I19" s="212"/>
+      <c r="J19" s="198"/>
+      <c r="K19" s="207"/>
     </row>
     <row r="20" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="95">
@@ -5554,9 +5467,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="27"/>
       <c r="H20" s="28"/>
-      <c r="I20" s="211"/>
-      <c r="J20" s="197"/>
-      <c r="K20" s="206"/>
+      <c r="I20" s="212"/>
+      <c r="J20" s="198"/>
+      <c r="K20" s="207"/>
     </row>
     <row r="21" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="89">
@@ -5576,9 +5489,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="27"/>
       <c r="H21" s="28"/>
-      <c r="I21" s="211"/>
-      <c r="J21" s="197"/>
-      <c r="K21" s="206"/>
+      <c r="I21" s="212"/>
+      <c r="J21" s="198"/>
+      <c r="K21" s="207"/>
     </row>
     <row r="22" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="89">
@@ -5598,9 +5511,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="27"/>
       <c r="H22" s="28"/>
-      <c r="I22" s="211"/>
-      <c r="J22" s="197"/>
-      <c r="K22" s="206"/>
+      <c r="I22" s="212"/>
+      <c r="J22" s="198"/>
+      <c r="K22" s="207"/>
     </row>
     <row r="23" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="89">
@@ -5620,9 +5533,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
-      <c r="I23" s="211"/>
-      <c r="J23" s="197"/>
-      <c r="K23" s="206"/>
+      <c r="I23" s="212"/>
+      <c r="J23" s="198"/>
+      <c r="K23" s="207"/>
     </row>
     <row r="24" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="89">
@@ -5642,9 +5555,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
-      <c r="I24" s="211"/>
-      <c r="J24" s="197"/>
-      <c r="K24" s="206"/>
+      <c r="I24" s="212"/>
+      <c r="J24" s="198"/>
+      <c r="K24" s="207"/>
     </row>
     <row r="25" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="89">
@@ -5664,9 +5577,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="27"/>
       <c r="H25" s="28"/>
-      <c r="I25" s="211"/>
-      <c r="J25" s="197"/>
-      <c r="K25" s="206"/>
+      <c r="I25" s="212"/>
+      <c r="J25" s="198"/>
+      <c r="K25" s="207"/>
     </row>
     <row r="26" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="89">
@@ -5686,9 +5599,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="27"/>
       <c r="H26" s="28"/>
-      <c r="I26" s="211"/>
-      <c r="J26" s="197"/>
-      <c r="K26" s="206"/>
+      <c r="I26" s="212"/>
+      <c r="J26" s="198"/>
+      <c r="K26" s="207"/>
     </row>
     <row r="27" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="89">
@@ -5708,9 +5621,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28"/>
-      <c r="I27" s="211"/>
-      <c r="J27" s="197"/>
-      <c r="K27" s="206"/>
+      <c r="I27" s="212"/>
+      <c r="J27" s="198"/>
+      <c r="K27" s="207"/>
     </row>
     <row r="28" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="89">
@@ -5730,9 +5643,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="27"/>
       <c r="H28" s="28"/>
-      <c r="I28" s="211"/>
-      <c r="J28" s="197"/>
-      <c r="K28" s="206"/>
+      <c r="I28" s="212"/>
+      <c r="J28" s="198"/>
+      <c r="K28" s="207"/>
     </row>
     <row r="29" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="89">
@@ -5752,9 +5665,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="27"/>
       <c r="H29" s="28"/>
-      <c r="I29" s="211"/>
-      <c r="J29" s="197"/>
-      <c r="K29" s="206"/>
+      <c r="I29" s="212"/>
+      <c r="J29" s="198"/>
+      <c r="K29" s="207"/>
     </row>
     <row r="30" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="95">
@@ -5774,9 +5687,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="27"/>
       <c r="H30" s="28"/>
-      <c r="I30" s="211"/>
-      <c r="J30" s="197"/>
-      <c r="K30" s="206"/>
+      <c r="I30" s="212"/>
+      <c r="J30" s="198"/>
+      <c r="K30" s="207"/>
     </row>
     <row r="31" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="89">
@@ -5796,9 +5709,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="27"/>
       <c r="H31" s="28"/>
-      <c r="I31" s="211"/>
-      <c r="J31" s="197"/>
-      <c r="K31" s="206"/>
+      <c r="I31" s="212"/>
+      <c r="J31" s="198"/>
+      <c r="K31" s="207"/>
     </row>
     <row r="32" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="89">
@@ -5818,9 +5731,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="27"/>
       <c r="H32" s="28"/>
-      <c r="I32" s="211"/>
-      <c r="J32" s="197"/>
-      <c r="K32" s="206"/>
+      <c r="I32" s="212"/>
+      <c r="J32" s="198"/>
+      <c r="K32" s="207"/>
     </row>
     <row r="33" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="89">
@@ -5840,9 +5753,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="27"/>
       <c r="H33" s="28"/>
-      <c r="I33" s="211"/>
-      <c r="J33" s="197"/>
-      <c r="K33" s="206"/>
+      <c r="I33" s="212"/>
+      <c r="J33" s="198"/>
+      <c r="K33" s="207"/>
     </row>
     <row r="34" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="89">
@@ -5862,9 +5775,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="27"/>
       <c r="H34" s="28"/>
-      <c r="I34" s="211"/>
-      <c r="J34" s="197"/>
-      <c r="K34" s="206"/>
+      <c r="I34" s="212"/>
+      <c r="J34" s="198"/>
+      <c r="K34" s="207"/>
     </row>
     <row r="35" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="89">
@@ -5884,9 +5797,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="27"/>
       <c r="H35" s="28"/>
-      <c r="I35" s="211"/>
-      <c r="J35" s="197"/>
-      <c r="K35" s="206"/>
+      <c r="I35" s="212"/>
+      <c r="J35" s="198"/>
+      <c r="K35" s="207"/>
     </row>
     <row r="36" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="89">
@@ -5906,9 +5819,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="27"/>
       <c r="H36" s="28"/>
-      <c r="I36" s="211"/>
-      <c r="J36" s="197"/>
-      <c r="K36" s="206"/>
+      <c r="I36" s="212"/>
+      <c r="J36" s="198"/>
+      <c r="K36" s="207"/>
     </row>
     <row r="37" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="89">
@@ -5928,9 +5841,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="27"/>
       <c r="H37" s="28"/>
-      <c r="I37" s="211"/>
-      <c r="J37" s="197"/>
-      <c r="K37" s="206"/>
+      <c r="I37" s="212"/>
+      <c r="J37" s="198"/>
+      <c r="K37" s="207"/>
     </row>
     <row r="38" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="89">
@@ -5950,9 +5863,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="27"/>
       <c r="H38" s="28"/>
-      <c r="I38" s="211"/>
-      <c r="J38" s="197"/>
-      <c r="K38" s="206"/>
+      <c r="I38" s="212"/>
+      <c r="J38" s="198"/>
+      <c r="K38" s="207"/>
     </row>
     <row r="39" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="96">
@@ -5972,16 +5885,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="27"/>
       <c r="H39" s="28"/>
-      <c r="I39" s="211"/>
-      <c r="J39" s="197"/>
-      <c r="K39" s="206"/>
+      <c r="I39" s="212"/>
+      <c r="J39" s="198"/>
+      <c r="K39" s="207"/>
     </row>
     <row r="40" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="235" t="s">
+      <c r="A40" s="236" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="236"/>
-      <c r="C40" s="236"/>
+      <c r="B40" s="237"/>
+      <c r="C40" s="237"/>
       <c r="D40" s="29" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -6002,16 +5915,16 @@
         <f>AVERAGE(H10:H39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="197"/>
-      <c r="J40" s="197"/>
-      <c r="K40" s="206"/>
+      <c r="I40" s="198"/>
+      <c r="J40" s="198"/>
+      <c r="K40" s="207"/>
     </row>
     <row r="41" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="220" t="s">
+      <c r="A41" s="221" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="221"/>
-      <c r="C41" s="221"/>
+      <c r="B41" s="222"/>
+      <c r="C41" s="222"/>
       <c r="D41" s="32">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -6032,16 +5945,16 @@
         <f>MIN(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="197"/>
-      <c r="J41" s="197"/>
-      <c r="K41" s="206"/>
+      <c r="I41" s="198"/>
+      <c r="J41" s="198"/>
+      <c r="K41" s="207"/>
     </row>
     <row r="42" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="215" t="s">
+      <c r="A42" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="216"/>
-      <c r="C42" s="216"/>
+      <c r="B42" s="217"/>
+      <c r="C42" s="217"/>
       <c r="D42" s="35">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -6062,16 +5975,16 @@
         <f>MAX(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="199"/>
-      <c r="J42" s="199"/>
-      <c r="K42" s="207"/>
+      <c r="I42" s="200"/>
+      <c r="J42" s="200"/>
+      <c r="K42" s="208"/>
     </row>
     <row r="43" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="150"/>
-      <c r="C43" s="150"/>
+      <c r="B43" s="151"/>
+      <c r="C43" s="151"/>
       <c r="D43" s="38" t="s">
         <v>22</v>
       </c>
@@ -6088,8 +6001,8 @@
     </row>
     <row r="44" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="43"/>
-      <c r="B44" s="149"/>
-      <c r="C44" s="149"/>
+      <c r="B44" s="150"/>
+      <c r="C44" s="150"/>
       <c r="D44" s="38"/>
       <c r="F44" s="39"/>
       <c r="G44" s="40"/>
@@ -6098,15 +6011,15 @@
       <c r="J44" s="17"/>
     </row>
     <row r="45" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="132" t="s">
+      <c r="A45" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="132"/>
-      <c r="C45" s="132"/>
+      <c r="B45" s="133"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
       <c r="F45" s="40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G45" s="39">
         <f>Page1!G44</f>
@@ -6115,11 +6028,11 @@
       <c r="H45" s="38"/>
     </row>
     <row r="46" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="132" t="s">
-        <v>133</v>
-      </c>
-      <c r="B46" s="132"/>
-      <c r="C46" s="132"/>
+      <c r="A46" s="133" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
       <c r="D46" s="38"/>
       <c r="E46" s="38"/>
       <c r="F46" s="38"/>
@@ -6172,8 +6085,8 @@
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="notBetween">
-      <formula>52</formula>
-      <formula>64</formula>
+      <formula>54</formula>
+      <formula>63</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E42">
@@ -6184,8 +6097,8 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F42">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="notBetween">
-      <formula>-12.5</formula>
-      <formula>-4.5</formula>
+      <formula>-11.5</formula>
+      <formula>-5.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:H42">
@@ -6215,15 +6128,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="242" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="243"/>
+      <c r="B1" s="243"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="243"/>
+      <c r="F1" s="243"/>
+      <c r="G1" s="244"/>
     </row>
     <row r="2" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="100"/>
@@ -6237,37 +6150,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="286" t="s">
-        <v>138</v>
-      </c>
-      <c r="B3" s="287"/>
-      <c r="C3" s="287"/>
-      <c r="D3" s="287"/>
-      <c r="E3" s="287"/>
-      <c r="F3" s="287"/>
-      <c r="G3" s="288"/>
+      <c r="A3" s="287" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="288"/>
+      <c r="C3" s="288"/>
+      <c r="D3" s="288"/>
+      <c r="E3" s="288"/>
+      <c r="F3" s="288"/>
+      <c r="G3" s="289"/>
     </row>
     <row r="4" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="211" t="s">
+      <c r="A4" s="212" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="206"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="207"/>
     </row>
     <row r="5" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="283" t="s">
+      <c r="A5" s="284" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="284"/>
-      <c r="C5" s="284"/>
-      <c r="D5" s="284"/>
-      <c r="E5" s="284"/>
-      <c r="F5" s="284"/>
-      <c r="G5" s="285"/>
+      <c r="B5" s="285"/>
+      <c r="C5" s="285"/>
+      <c r="D5" s="285"/>
+      <c r="E5" s="285"/>
+      <c r="F5" s="285"/>
+      <c r="G5" s="286"/>
     </row>
     <row r="6" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103" t="s">
@@ -6279,14 +6192,14 @@
       <c r="C6" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="244" t="s">
+      <c r="D6" s="245" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="245"/>
-      <c r="F6" s="237" t="s">
+      <c r="E6" s="246"/>
+      <c r="F6" s="238" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="246">
+      <c r="G6" s="247">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -6299,13 +6212,13 @@
       <c r="C7" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="244">
+      <c r="D7" s="245">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="245"/>
-      <c r="F7" s="237"/>
-      <c r="G7" s="247"/>
+      <c r="E7" s="246"/>
+      <c r="F7" s="238"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="1:7" s="99" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="103" t="s">
@@ -6318,15 +6231,15 @@
       <c r="C8" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="237">
+      <c r="D8" s="238">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="237"/>
-      <c r="F8" s="238" t="s">
+      <c r="E8" s="238"/>
+      <c r="F8" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="246">
+      <c r="G8" s="247">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -6339,15 +6252,15 @@
         <f>Page1!G44</f>
         <v>461303600</v>
       </c>
-      <c r="C9" s="238" t="s">
+      <c r="C9" s="239" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="293" t="s">
+      <c r="D9" s="294" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="294"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="291"/>
+      <c r="E9" s="295"/>
+      <c r="F9" s="240"/>
+      <c r="G9" s="292"/>
     </row>
     <row r="10" spans="1:7" s="99" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="110" t="s">
@@ -6357,34 +6270,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="240"/>
-      <c r="D10" s="295"/>
-      <c r="E10" s="296"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="292"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="296"/>
+      <c r="E10" s="297"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="293"/>
     </row>
     <row r="11" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="297" t="s">
+      <c r="A11" s="298" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="299" t="s">
+      <c r="B11" s="300" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="301" t="s">
+      <c r="C11" s="302" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="302"/>
-      <c r="E11" s="303"/>
-      <c r="F11" s="299" t="s">
+      <c r="D11" s="303"/>
+      <c r="E11" s="304"/>
+      <c r="F11" s="300" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="304" t="s">
+      <c r="G11" s="305" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="298"/>
-      <c r="B12" s="300"/>
+      <c r="A12" s="299"/>
+      <c r="B12" s="301"/>
       <c r="C12" s="112" t="s">
         <v>63</v>
       </c>
@@ -6394,8 +6307,8 @@
       <c r="E12" s="112" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="300"/>
-      <c r="G12" s="305"/>
+      <c r="F12" s="301"/>
+      <c r="G12" s="306"/>
     </row>
     <row r="13" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="113" t="s">
@@ -6465,7 +6378,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="248" t="s">
+      <c r="G15" s="249" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6489,7 +6402,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="230"/>
+      <c r="G16" s="231"/>
     </row>
     <row r="17" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="117" t="s">
@@ -6511,7 +6424,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="230"/>
+      <c r="G17" s="231"/>
     </row>
     <row r="18" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="117" t="s">
@@ -6533,7 +6446,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="230"/>
+      <c r="G18" s="231"/>
     </row>
     <row r="19" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="117" t="s">
@@ -6555,7 +6468,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="230"/>
+      <c r="G19" s="231"/>
     </row>
     <row r="20" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="117" t="s">
@@ -6577,7 +6490,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="230"/>
+      <c r="G20" s="231"/>
     </row>
     <row r="21" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="117" t="s">
@@ -6599,7 +6512,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="230"/>
+      <c r="G21" s="231"/>
     </row>
     <row r="22" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="117" t="s">
@@ -6621,7 +6534,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="166"/>
+      <c r="G22" s="167"/>
     </row>
     <row r="23" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="117" t="s">
@@ -6721,26 +6634,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="249" t="s">
+      <c r="A27" s="250" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="250"/>
-      <c r="C27" s="250"/>
-      <c r="D27" s="250"/>
-      <c r="E27" s="250"/>
-      <c r="F27" s="250"/>
-      <c r="G27" s="251"/>
+      <c r="B27" s="251"/>
+      <c r="C27" s="251"/>
+      <c r="D27" s="251"/>
+      <c r="E27" s="251"/>
+      <c r="F27" s="251"/>
+      <c r="G27" s="252"/>
     </row>
     <row r="28" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="252" t="s">
+      <c r="A28" s="253" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="253"/>
-      <c r="C28" s="254" t="s">
+      <c r="B28" s="254"/>
+      <c r="C28" s="255" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="255"/>
-      <c r="E28" s="256"/>
+      <c r="D28" s="256"/>
+      <c r="E28" s="257"/>
       <c r="F28" s="126" t="s">
         <v>96</v>
       </c>
@@ -6749,15 +6662,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="257" t="s">
+      <c r="A29" s="258" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="245"/>
-      <c r="C29" s="258" t="s">
+      <c r="B29" s="246"/>
+      <c r="C29" s="259" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="259"/>
-      <c r="E29" s="260"/>
+      <c r="D29" s="260"/>
+      <c r="E29" s="261"/>
       <c r="F29" s="60" t="s">
         <v>96</v>
       </c>
@@ -6766,15 +6679,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="257" t="s">
+      <c r="A30" s="258" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="245"/>
-      <c r="C30" s="258" t="s">
+      <c r="B30" s="246"/>
+      <c r="C30" s="259" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="259"/>
-      <c r="E30" s="260"/>
+      <c r="D30" s="260"/>
+      <c r="E30" s="261"/>
       <c r="F30" s="60" t="s">
         <v>96</v>
       </c>
@@ -6783,15 +6696,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="257" t="s">
+      <c r="A31" s="258" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="245"/>
-      <c r="C31" s="258" t="s">
+      <c r="B31" s="246"/>
+      <c r="C31" s="259" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="259"/>
-      <c r="E31" s="260"/>
+      <c r="D31" s="260"/>
+      <c r="E31" s="261"/>
       <c r="F31" s="60" t="s">
         <v>96</v>
       </c>
@@ -6800,15 +6713,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="257" t="s">
+      <c r="A32" s="258" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="245"/>
-      <c r="C32" s="258" t="s">
+      <c r="B32" s="246"/>
+      <c r="C32" s="259" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="259"/>
-      <c r="E32" s="260"/>
+      <c r="D32" s="260"/>
+      <c r="E32" s="261"/>
       <c r="F32" s="60" t="s">
         <v>96</v>
       </c>
@@ -6816,61 +6729,61 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="257" t="s">
+    <row r="33" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="258" t="s">
         <v>107</v>
       </c>
-      <c r="B33" s="245"/>
-      <c r="C33" s="258" t="s">
+      <c r="B33" s="246"/>
+      <c r="C33" s="259" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="259"/>
-      <c r="E33" s="260"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="261"/>
       <c r="F33" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="G33" s="67" t="s">
+      <c r="G33" s="121" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="99" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="158" t="s">
+      <c r="A34" s="159" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="159"/>
-      <c r="C34" s="263" t="s">
+      <c r="B34" s="160"/>
+      <c r="C34" s="264" t="s">
         <v>110</v>
       </c>
-      <c r="D34" s="264"/>
-      <c r="E34" s="265"/>
+      <c r="D34" s="265"/>
+      <c r="E34" s="266"/>
       <c r="F34" s="127" t="s">
         <v>96</v>
       </c>
-      <c r="G34" s="67" t="s">
+      <c r="G34" s="132" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="249" t="s">
+      <c r="A35" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="B35" s="250"/>
-      <c r="C35" s="250"/>
-      <c r="D35" s="250"/>
-      <c r="E35" s="250"/>
-      <c r="F35" s="250"/>
-      <c r="G35" s="251"/>
+      <c r="B35" s="251"/>
+      <c r="C35" s="251"/>
+      <c r="D35" s="251"/>
+      <c r="E35" s="251"/>
+      <c r="F35" s="251"/>
+      <c r="G35" s="252"/>
     </row>
     <row r="36" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="152" t="s">
+      <c r="A36" s="153" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="153"/>
-      <c r="C36" s="261" t="s">
+      <c r="B36" s="154"/>
+      <c r="C36" s="262" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="262"/>
-      <c r="E36" s="153"/>
+      <c r="D36" s="263"/>
+      <c r="E36" s="154"/>
       <c r="F36" s="10" t="s">
         <v>96</v>
       </c>
@@ -6879,15 +6792,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="252" t="s">
+      <c r="A37" s="253" t="s">
         <v>113</v>
       </c>
-      <c r="B37" s="253"/>
-      <c r="C37" s="244" t="s">
+      <c r="B37" s="254"/>
+      <c r="C37" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="267"/>
-      <c r="E37" s="245"/>
+      <c r="D37" s="268"/>
+      <c r="E37" s="246"/>
       <c r="F37" s="119" t="s">
         <v>96</v>
       </c>
@@ -6896,15 +6809,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="257" t="s">
+      <c r="A38" s="258" t="s">
         <v>115</v>
       </c>
-      <c r="B38" s="245"/>
-      <c r="C38" s="244" t="s">
+      <c r="B38" s="246"/>
+      <c r="C38" s="245" t="s">
         <v>116</v>
       </c>
-      <c r="D38" s="267"/>
-      <c r="E38" s="245"/>
+      <c r="D38" s="268"/>
+      <c r="E38" s="246"/>
       <c r="F38" s="119" t="s">
         <v>96</v>
       </c>
@@ -6913,15 +6826,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="158" t="s">
+      <c r="A39" s="159" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="159"/>
-      <c r="C39" s="289" t="s">
+      <c r="B39" s="160"/>
+      <c r="C39" s="290" t="s">
         <v>118</v>
       </c>
-      <c r="D39" s="290"/>
-      <c r="E39" s="159"/>
+      <c r="D39" s="291"/>
+      <c r="E39" s="160"/>
       <c r="F39" s="1" t="s">
         <v>96</v>
       </c>
@@ -6930,50 +6843,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="268" t="s">
+      <c r="A40" s="269" t="s">
         <v>119</v>
       </c>
-      <c r="B40" s="269"/>
-      <c r="C40" s="270" t="s">
+      <c r="B40" s="270"/>
+      <c r="C40" s="271" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" s="272"/>
+      <c r="E40" s="273"/>
+      <c r="F40" s="271" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40" s="273"/>
+    </row>
+    <row r="41" spans="1:7" s="99" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="274"/>
+      <c r="B41" s="275"/>
+      <c r="C41" s="212"/>
+      <c r="D41" s="198"/>
+      <c r="E41" s="207"/>
+      <c r="F41" s="278"/>
+      <c r="G41" s="279"/>
+    </row>
+    <row r="42" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="276"/>
+      <c r="B42" s="277"/>
+      <c r="C42" s="280" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="281"/>
+      <c r="E42" s="282"/>
+      <c r="F42" s="280" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="271"/>
-      <c r="E40" s="272"/>
-      <c r="F40" s="270" t="s">
-        <v>140</v>
-      </c>
-      <c r="G40" s="272"/>
-    </row>
-    <row r="41" spans="1:7" s="99" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="273"/>
-      <c r="B41" s="274"/>
-      <c r="C41" s="211"/>
-      <c r="D41" s="197"/>
-      <c r="E41" s="206"/>
-      <c r="F41" s="277"/>
-      <c r="G41" s="278"/>
-    </row>
-    <row r="42" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="275"/>
-      <c r="B42" s="276"/>
-      <c r="C42" s="279" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="280"/>
-      <c r="E42" s="281"/>
-      <c r="F42" s="279" t="s">
-        <v>141</v>
-      </c>
-      <c r="G42" s="281"/>
+      <c r="G42" s="282"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="128"/>
       <c r="B43" s="128"/>
       <c r="C43" s="128"/>
       <c r="D43" s="128"/>
-      <c r="E43" s="306"/>
-      <c r="F43" s="306"/>
-      <c r="G43" s="306"/>
+      <c r="E43" s="307"/>
+      <c r="F43" s="307"/>
+      <c r="G43" s="307"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
@@ -6982,21 +6895,21 @@
       <c r="B44" s="129"/>
       <c r="C44" s="131"/>
       <c r="D44" s="128"/>
-      <c r="E44" s="266"/>
-      <c r="F44" s="266"/>
-      <c r="G44" s="266"/>
+      <c r="E44" s="267"/>
+      <c r="F44" s="267"/>
+      <c r="G44" s="267"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="282" t="s">
+      <c r="A46" s="283" t="s">
         <v>121</v>
       </c>
-      <c r="B46" s="282"/>
+      <c r="B46" s="283"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="282" t="s">
+      <c r="A47" s="283" t="s">
         <v>122</v>
       </c>
-      <c r="B47" s="282"/>
+      <c r="B47" s="283"/>
     </row>
   </sheetData>
   <mergeCells count="55">

--- a/backend/templates/UC-18gsm-250P-ABQR.xlsx
+++ b/backend/templates/UC-18gsm-250P-ABQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D54676-1AE9-40A9-A7F7-0AFE915A2CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31E0DFD-7725-4E2F-BBC0-22D55FE6D563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="142">
   <si>
     <t>Sample No.</t>
   </si>
@@ -203,9 +203,6 @@
   </si>
   <si>
     <t>Unicharm</t>
-  </si>
-  <si>
-    <t># 02</t>
   </si>
   <si>
     <t xml:space="preserve">Production Date </t>
@@ -1871,6 +1868,78 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1886,15 +1955,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1928,106 +1991,128 @@
     <xf numFmtId="49" fontId="6" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2036,6 +2121,10 @@
     <xf numFmtId="1" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2048,168 +2137,262 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2221,194 +2404,8 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2978,35 +2975,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
       <c r="K1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
       <c r="K2" s="16" t="s">
         <v>29</v>
       </c>
@@ -3027,12 +3024,12 @@
       <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:13" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="153" t="s">
+      <c r="A4" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="161"/>
-      <c r="D4" s="162"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="145"/>
       <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3044,19 +3041,19 @@
       <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="168"/>
-      <c r="K4" s="169"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="152"/>
       <c r="M4" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="15" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="159" t="s">
+      <c r="A5" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="160"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="164"/>
+      <c r="B5" s="143"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="147"/>
       <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
@@ -3068,28 +3065,28 @@
       <c r="I5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="170"/>
-      <c r="K5" s="171"/>
+      <c r="J5" s="153"/>
+      <c r="K5" s="154"/>
     </row>
     <row r="6" spans="1:13" s="15" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="134" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="135"/>
-      <c r="C6" s="136"/>
+      <c r="A6" s="156" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="157"/>
+      <c r="C6" s="158"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" s="157"/>
-      <c r="H6" s="158"/>
-      <c r="I6" s="157"/>
-      <c r="J6" s="165"/>
-      <c r="K6" s="166"/>
+        <v>139</v>
+      </c>
+      <c r="G6" s="140"/>
+      <c r="H6" s="141"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="149"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="159" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="138"/>
@@ -3103,29 +3100,29 @@
       <c r="F7" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="155" t="s">
+      <c r="G7" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="155" t="s">
-        <v>127</v>
+      <c r="H7" s="136" t="s">
+        <v>126</v>
       </c>
       <c r="I7" s="138" t="s">
         <v>1</v>
       </c>
       <c r="J7" s="138"/>
-      <c r="K7" s="167"/>
+      <c r="K7" s="150"/>
     </row>
     <row r="8" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="139"/>
-      <c r="B8" s="140"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140" t="s">
+      <c r="A8" s="160"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="140"/>
-      <c r="G8" s="156"/>
-      <c r="H8" s="156"/>
+      <c r="F8" s="139"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="137"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3527,11 +3524,11 @@
       <c r="K38" s="72"/>
     </row>
     <row r="39" spans="1:14" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="147" t="s">
+      <c r="A39" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="148"/>
-      <c r="C39" s="149"/>
+      <c r="B39" s="168"/>
+      <c r="C39" s="169"/>
       <c r="D39" s="30" t="e">
         <f t="shared" ref="D39:K39" si="0">AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3566,11 +3563,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="144" t="s">
+      <c r="A40" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="145"/>
-      <c r="C40" s="146"/>
+      <c r="B40" s="165"/>
+      <c r="C40" s="166"/>
       <c r="D40" s="33">
         <f t="shared" ref="D40:K40" si="1">MIN(D9:D38)</f>
         <v>0</v>
@@ -3605,11 +3602,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="141" t="s">
+      <c r="A41" s="161" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="142"/>
-      <c r="C41" s="143"/>
+      <c r="B41" s="162"/>
+      <c r="C41" s="163"/>
       <c r="D41" s="79">
         <f t="shared" ref="D41:K41" si="2">MAX(D9:D38)</f>
         <v>0</v>
@@ -3650,8 +3647,8 @@
       <c r="A42" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="151"/>
-      <c r="C42" s="151"/>
+      <c r="B42" s="171"/>
+      <c r="C42" s="171"/>
       <c r="D42" s="38" t="s">
         <v>22</v>
       </c>
@@ -3668,8 +3665,8 @@
     </row>
     <row r="43" spans="1:14" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="43"/>
-      <c r="B43" s="150"/>
-      <c r="C43" s="150"/>
+      <c r="B43" s="170"/>
+      <c r="C43" s="170"/>
       <c r="D43" s="38"/>
       <c r="F43" s="39"/>
       <c r="G43" s="40"/>
@@ -3678,15 +3675,15 @@
       <c r="J43" s="17"/>
     </row>
     <row r="44" spans="1:14" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="133" t="s">
+      <c r="A44" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="133"/>
-      <c r="C44" s="133"/>
+      <c r="B44" s="155"/>
+      <c r="C44" s="155"/>
       <c r="D44" s="38"/>
       <c r="E44" s="38"/>
       <c r="F44" s="40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G44" s="39">
         <v>461303600</v>
@@ -3694,11 +3691,11 @@
       <c r="H44" s="38"/>
     </row>
     <row r="45" spans="1:14" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="133" t="s">
-        <v>131</v>
-      </c>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
+      <c r="A45" s="155" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" s="155"/>
+      <c r="C45" s="155"/>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
       <c r="F45" s="38"/>
@@ -3727,6 +3724,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="25">
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:B4"/>
@@ -3742,16 +3749,6 @@
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B42:C42"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:D41">
     <cfRule type="cellIs" dxfId="17" priority="19" operator="notBetween">
@@ -3818,35 +3815,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
       <c r="K1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
       <c r="K2" s="16" t="s">
         <v>29</v>
       </c>
@@ -3867,18 +3864,18 @@
       <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="153" t="s">
+      <c r="A4" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="154">
+      <c r="B4" s="135">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="209">
+      <c r="C4" s="205">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="210"/>
+      <c r="D4" s="181"/>
       <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3896,25 +3893,25 @@
       <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201">
+      <c r="J4" s="198">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="202"/>
+      <c r="K4" s="199"/>
     </row>
     <row r="5" spans="1:11" s="15" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="159" t="s">
+      <c r="A5" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="160">
+      <c r="B5" s="143">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="163">
+      <c r="C5" s="146">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="164"/>
+      <c r="D5" s="147"/>
       <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
@@ -3932,104 +3929,104 @@
       <c r="I5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="203">
+      <c r="J5" s="200">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="204"/>
+      <c r="K5" s="201"/>
     </row>
     <row r="6" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="213" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="214"/>
-      <c r="C6" s="215"/>
-      <c r="D6" s="211"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="195"/>
-      <c r="G6" s="194"/>
-      <c r="H6" s="195"/>
-      <c r="I6" s="192"/>
-      <c r="J6" s="193"/>
+      <c r="A6" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="173"/>
+      <c r="C6" s="174"/>
+      <c r="D6" s="175"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="193"/>
+      <c r="H6" s="177"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="192"/>
       <c r="K6" s="20"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="211" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="196"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="218" t="s">
+      <c r="A7" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="176"/>
+      <c r="C7" s="176"/>
+      <c r="D7" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="196"/>
-      <c r="F7" s="210"/>
-      <c r="G7" s="194" t="s">
+      <c r="E7" s="176"/>
+      <c r="F7" s="181"/>
+      <c r="G7" s="193" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="196"/>
-      <c r="I7" s="194" t="s">
-        <v>133</v>
-      </c>
-      <c r="J7" s="195"/>
-      <c r="K7" s="206" t="s">
-        <v>126</v>
+      <c r="H7" s="176"/>
+      <c r="I7" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="J7" s="177"/>
+      <c r="K7" s="202" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="212"/>
-      <c r="B8" s="198"/>
-      <c r="C8" s="198"/>
-      <c r="D8" s="212" t="s">
+      <c r="A8" s="186"/>
+      <c r="B8" s="195"/>
+      <c r="C8" s="195"/>
+      <c r="D8" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="224" t="s">
+      <c r="E8" s="188" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="205" t="s">
+      <c r="F8" s="189" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="197"/>
-      <c r="H8" s="198"/>
-      <c r="I8" s="197" t="s">
-        <v>132</v>
-      </c>
-      <c r="J8" s="205"/>
-      <c r="K8" s="207"/>
+      <c r="G8" s="194"/>
+      <c r="H8" s="195"/>
+      <c r="I8" s="194" t="s">
+        <v>131</v>
+      </c>
+      <c r="J8" s="189"/>
+      <c r="K8" s="203"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="212"/>
-      <c r="B9" s="198"/>
-      <c r="C9" s="198"/>
-      <c r="D9" s="212"/>
-      <c r="E9" s="155"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="197"/>
-      <c r="H9" s="198"/>
+      <c r="A9" s="186"/>
+      <c r="B9" s="195"/>
+      <c r="C9" s="195"/>
+      <c r="D9" s="186"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="189"/>
+      <c r="G9" s="194"/>
+      <c r="H9" s="195"/>
       <c r="I9" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J9" s="48">
         <v>250</v>
       </c>
-      <c r="K9" s="207"/>
+      <c r="K9" s="203"/>
     </row>
     <row r="10" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="212"/>
-      <c r="B10" s="198"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="156"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="199"/>
-      <c r="H10" s="200"/>
+      <c r="A10" s="186"/>
+      <c r="B10" s="195"/>
+      <c r="C10" s="195"/>
+      <c r="D10" s="187"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="196"/>
+      <c r="H10" s="197"/>
       <c r="I10" s="49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J10" s="50">
         <v>253</v>
       </c>
-      <c r="K10" s="208"/>
+      <c r="K10" s="204"/>
     </row>
     <row r="11" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="86">
@@ -4047,10 +4044,10 @@
       <c r="D11" s="51"/>
       <c r="E11" s="52"/>
       <c r="F11" s="52"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="188"/>
-      <c r="J11" s="189"/>
+      <c r="G11" s="221"/>
+      <c r="H11" s="221"/>
+      <c r="I11" s="206"/>
+      <c r="J11" s="207"/>
       <c r="K11" s="53"/>
     </row>
     <row r="12" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4069,10 +4066,10 @@
       <c r="D12" s="54"/>
       <c r="E12" s="55"/>
       <c r="F12" s="55"/>
-      <c r="G12" s="177"/>
-      <c r="H12" s="177"/>
-      <c r="I12" s="174"/>
-      <c r="J12" s="175"/>
+      <c r="G12" s="214"/>
+      <c r="H12" s="214"/>
+      <c r="I12" s="208"/>
+      <c r="J12" s="209"/>
       <c r="K12" s="56"/>
     </row>
     <row r="13" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4091,10 +4088,10 @@
       <c r="D13" s="54"/>
       <c r="E13" s="55"/>
       <c r="F13" s="55"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="177"/>
-      <c r="I13" s="174"/>
-      <c r="J13" s="175"/>
+      <c r="G13" s="214"/>
+      <c r="H13" s="214"/>
+      <c r="I13" s="208"/>
+      <c r="J13" s="209"/>
       <c r="K13" s="56"/>
     </row>
     <row r="14" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4113,10 +4110,10 @@
       <c r="D14" s="54"/>
       <c r="E14" s="55"/>
       <c r="F14" s="55"/>
-      <c r="G14" s="177"/>
-      <c r="H14" s="177"/>
-      <c r="I14" s="174"/>
-      <c r="J14" s="175"/>
+      <c r="G14" s="214"/>
+      <c r="H14" s="214"/>
+      <c r="I14" s="208"/>
+      <c r="J14" s="209"/>
       <c r="K14" s="56"/>
     </row>
     <row r="15" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4135,10 +4132,10 @@
       <c r="D15" s="54"/>
       <c r="E15" s="55"/>
       <c r="F15" s="55"/>
-      <c r="G15" s="177"/>
-      <c r="H15" s="177"/>
-      <c r="I15" s="174"/>
-      <c r="J15" s="175"/>
+      <c r="G15" s="214"/>
+      <c r="H15" s="214"/>
+      <c r="I15" s="208"/>
+      <c r="J15" s="209"/>
       <c r="K15" s="56"/>
     </row>
     <row r="16" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4157,10 +4154,10 @@
       <c r="D16" s="51"/>
       <c r="E16" s="52"/>
       <c r="F16" s="52"/>
-      <c r="G16" s="176"/>
-      <c r="H16" s="176"/>
-      <c r="I16" s="174"/>
-      <c r="J16" s="175"/>
+      <c r="G16" s="221"/>
+      <c r="H16" s="221"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="209"/>
       <c r="K16" s="53"/>
     </row>
     <row r="17" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4179,10 +4176,10 @@
       <c r="D17" s="54"/>
       <c r="E17" s="55"/>
       <c r="F17" s="55"/>
-      <c r="G17" s="177"/>
-      <c r="H17" s="177"/>
-      <c r="I17" s="174"/>
-      <c r="J17" s="175"/>
+      <c r="G17" s="214"/>
+      <c r="H17" s="214"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="209"/>
       <c r="K17" s="56"/>
     </row>
     <row r="18" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4201,10 +4198,10 @@
       <c r="D18" s="54"/>
       <c r="E18" s="55"/>
       <c r="F18" s="55"/>
-      <c r="G18" s="177"/>
-      <c r="H18" s="177"/>
-      <c r="I18" s="174"/>
-      <c r="J18" s="175"/>
+      <c r="G18" s="214"/>
+      <c r="H18" s="214"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="209"/>
       <c r="K18" s="56"/>
     </row>
     <row r="19" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4223,10 +4220,10 @@
       <c r="D19" s="54"/>
       <c r="E19" s="55"/>
       <c r="F19" s="55"/>
-      <c r="G19" s="177"/>
-      <c r="H19" s="177"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="175"/>
+      <c r="G19" s="214"/>
+      <c r="H19" s="214"/>
+      <c r="I19" s="208"/>
+      <c r="J19" s="209"/>
       <c r="K19" s="56"/>
     </row>
     <row r="20" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4245,10 +4242,10 @@
       <c r="D20" s="54"/>
       <c r="E20" s="55"/>
       <c r="F20" s="55"/>
-      <c r="G20" s="172"/>
-      <c r="H20" s="173"/>
-      <c r="I20" s="174"/>
-      <c r="J20" s="175"/>
+      <c r="G20" s="219"/>
+      <c r="H20" s="220"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="209"/>
       <c r="K20" s="56"/>
     </row>
     <row r="21" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4267,10 +4264,10 @@
       <c r="D21" s="54"/>
       <c r="E21" s="55"/>
       <c r="F21" s="55"/>
-      <c r="G21" s="172"/>
-      <c r="H21" s="173"/>
-      <c r="I21" s="174"/>
-      <c r="J21" s="175"/>
+      <c r="G21" s="219"/>
+      <c r="H21" s="220"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="209"/>
       <c r="K21" s="56"/>
     </row>
     <row r="22" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4289,10 +4286,10 @@
       <c r="D22" s="54"/>
       <c r="E22" s="55"/>
       <c r="F22" s="55"/>
-      <c r="G22" s="172"/>
-      <c r="H22" s="173"/>
-      <c r="I22" s="174"/>
-      <c r="J22" s="175"/>
+      <c r="G22" s="219"/>
+      <c r="H22" s="220"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="209"/>
       <c r="K22" s="56"/>
     </row>
     <row r="23" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4311,10 +4308,10 @@
       <c r="D23" s="54"/>
       <c r="E23" s="55"/>
       <c r="F23" s="55"/>
-      <c r="G23" s="172"/>
-      <c r="H23" s="173"/>
-      <c r="I23" s="174"/>
-      <c r="J23" s="175"/>
+      <c r="G23" s="219"/>
+      <c r="H23" s="220"/>
+      <c r="I23" s="208"/>
+      <c r="J23" s="209"/>
       <c r="K23" s="56"/>
     </row>
     <row r="24" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4333,10 +4330,10 @@
       <c r="D24" s="54"/>
       <c r="E24" s="55"/>
       <c r="F24" s="55"/>
-      <c r="G24" s="172"/>
-      <c r="H24" s="173"/>
-      <c r="I24" s="174"/>
-      <c r="J24" s="175"/>
+      <c r="G24" s="219"/>
+      <c r="H24" s="220"/>
+      <c r="I24" s="208"/>
+      <c r="J24" s="209"/>
       <c r="K24" s="56"/>
     </row>
     <row r="25" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4355,10 +4352,10 @@
       <c r="D25" s="54"/>
       <c r="E25" s="55"/>
       <c r="F25" s="55"/>
-      <c r="G25" s="172"/>
-      <c r="H25" s="173"/>
-      <c r="I25" s="174"/>
-      <c r="J25" s="175"/>
+      <c r="G25" s="219"/>
+      <c r="H25" s="220"/>
+      <c r="I25" s="208"/>
+      <c r="J25" s="209"/>
       <c r="K25" s="56"/>
     </row>
     <row r="26" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4377,10 +4374,10 @@
       <c r="D26" s="54"/>
       <c r="E26" s="55"/>
       <c r="F26" s="55"/>
-      <c r="G26" s="172"/>
-      <c r="H26" s="173"/>
-      <c r="I26" s="174"/>
-      <c r="J26" s="175"/>
+      <c r="G26" s="219"/>
+      <c r="H26" s="220"/>
+      <c r="I26" s="208"/>
+      <c r="J26" s="209"/>
       <c r="K26" s="56"/>
     </row>
     <row r="27" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4399,10 +4396,10 @@
       <c r="D27" s="54"/>
       <c r="E27" s="55"/>
       <c r="F27" s="55"/>
-      <c r="G27" s="172"/>
-      <c r="H27" s="173"/>
-      <c r="I27" s="174"/>
-      <c r="J27" s="175"/>
+      <c r="G27" s="219"/>
+      <c r="H27" s="220"/>
+      <c r="I27" s="208"/>
+      <c r="J27" s="209"/>
       <c r="K27" s="56"/>
     </row>
     <row r="28" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4421,10 +4418,10 @@
       <c r="D28" s="54"/>
       <c r="E28" s="55"/>
       <c r="F28" s="55"/>
-      <c r="G28" s="172"/>
-      <c r="H28" s="173"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="175"/>
+      <c r="G28" s="219"/>
+      <c r="H28" s="220"/>
+      <c r="I28" s="208"/>
+      <c r="J28" s="209"/>
       <c r="K28" s="56"/>
     </row>
     <row r="29" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4443,10 +4440,10 @@
       <c r="D29" s="54"/>
       <c r="E29" s="55"/>
       <c r="F29" s="55"/>
-      <c r="G29" s="172"/>
-      <c r="H29" s="173"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="175"/>
+      <c r="G29" s="219"/>
+      <c r="H29" s="220"/>
+      <c r="I29" s="208"/>
+      <c r="J29" s="209"/>
       <c r="K29" s="56"/>
     </row>
     <row r="30" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4465,10 +4462,10 @@
       <c r="D30" s="54"/>
       <c r="E30" s="55"/>
       <c r="F30" s="55"/>
-      <c r="G30" s="172"/>
-      <c r="H30" s="173"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="175"/>
+      <c r="G30" s="219"/>
+      <c r="H30" s="220"/>
+      <c r="I30" s="208"/>
+      <c r="J30" s="209"/>
       <c r="K30" s="56"/>
     </row>
     <row r="31" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4487,10 +4484,10 @@
       <c r="D31" s="54"/>
       <c r="E31" s="55"/>
       <c r="F31" s="55"/>
-      <c r="G31" s="172"/>
-      <c r="H31" s="173"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="175"/>
+      <c r="G31" s="219"/>
+      <c r="H31" s="220"/>
+      <c r="I31" s="208"/>
+      <c r="J31" s="209"/>
       <c r="K31" s="56"/>
     </row>
     <row r="32" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4509,10 +4506,10 @@
       <c r="D32" s="54"/>
       <c r="E32" s="55"/>
       <c r="F32" s="55"/>
-      <c r="G32" s="172"/>
-      <c r="H32" s="173"/>
-      <c r="I32" s="174"/>
-      <c r="J32" s="175"/>
+      <c r="G32" s="219"/>
+      <c r="H32" s="220"/>
+      <c r="I32" s="208"/>
+      <c r="J32" s="209"/>
       <c r="K32" s="56"/>
     </row>
     <row r="33" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4531,10 +4528,10 @@
       <c r="D33" s="54"/>
       <c r="E33" s="55"/>
       <c r="F33" s="55"/>
-      <c r="G33" s="172"/>
-      <c r="H33" s="173"/>
-      <c r="I33" s="174"/>
-      <c r="J33" s="175"/>
+      <c r="G33" s="219"/>
+      <c r="H33" s="220"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="209"/>
       <c r="K33" s="56"/>
     </row>
     <row r="34" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4553,10 +4550,10 @@
       <c r="D34" s="54"/>
       <c r="E34" s="55"/>
       <c r="F34" s="55"/>
-      <c r="G34" s="172"/>
-      <c r="H34" s="173"/>
-      <c r="I34" s="174"/>
-      <c r="J34" s="175"/>
+      <c r="G34" s="219"/>
+      <c r="H34" s="220"/>
+      <c r="I34" s="208"/>
+      <c r="J34" s="209"/>
       <c r="K34" s="56"/>
     </row>
     <row r="35" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4575,10 +4572,10 @@
       <c r="D35" s="54"/>
       <c r="E35" s="55"/>
       <c r="F35" s="55"/>
-      <c r="G35" s="172"/>
-      <c r="H35" s="173"/>
-      <c r="I35" s="174"/>
-      <c r="J35" s="175"/>
+      <c r="G35" s="219"/>
+      <c r="H35" s="220"/>
+      <c r="I35" s="208"/>
+      <c r="J35" s="209"/>
       <c r="K35" s="56"/>
     </row>
     <row r="36" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4597,10 +4594,10 @@
       <c r="D36" s="54"/>
       <c r="E36" s="55"/>
       <c r="F36" s="55"/>
-      <c r="G36" s="172"/>
-      <c r="H36" s="173"/>
-      <c r="I36" s="174"/>
-      <c r="J36" s="175"/>
+      <c r="G36" s="219"/>
+      <c r="H36" s="220"/>
+      <c r="I36" s="208"/>
+      <c r="J36" s="209"/>
       <c r="K36" s="56"/>
     </row>
     <row r="37" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4619,10 +4616,10 @@
       <c r="D37" s="54"/>
       <c r="E37" s="55"/>
       <c r="F37" s="55"/>
-      <c r="G37" s="172"/>
-      <c r="H37" s="173"/>
-      <c r="I37" s="174"/>
-      <c r="J37" s="175"/>
+      <c r="G37" s="219"/>
+      <c r="H37" s="220"/>
+      <c r="I37" s="208"/>
+      <c r="J37" s="209"/>
       <c r="K37" s="56"/>
     </row>
     <row r="38" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4641,10 +4638,10 @@
       <c r="D38" s="54"/>
       <c r="E38" s="55"/>
       <c r="F38" s="55"/>
-      <c r="G38" s="172"/>
-      <c r="H38" s="173"/>
-      <c r="I38" s="174"/>
-      <c r="J38" s="175"/>
+      <c r="G38" s="219"/>
+      <c r="H38" s="220"/>
+      <c r="I38" s="208"/>
+      <c r="J38" s="209"/>
       <c r="K38" s="56"/>
     </row>
     <row r="39" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4663,10 +4660,10 @@
       <c r="D39" s="54"/>
       <c r="E39" s="55"/>
       <c r="F39" s="55"/>
-      <c r="G39" s="172"/>
-      <c r="H39" s="173"/>
-      <c r="I39" s="174"/>
-      <c r="J39" s="175"/>
+      <c r="G39" s="219"/>
+      <c r="H39" s="220"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="209"/>
       <c r="K39" s="56"/>
     </row>
     <row r="40" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4685,18 +4682,18 @@
       <c r="D40" s="54"/>
       <c r="E40" s="55"/>
       <c r="F40" s="55"/>
-      <c r="G40" s="177"/>
-      <c r="H40" s="177"/>
-      <c r="I40" s="174"/>
-      <c r="J40" s="175"/>
+      <c r="G40" s="214"/>
+      <c r="H40" s="214"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="209"/>
       <c r="K40" s="56"/>
     </row>
     <row r="41" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="219" t="s">
+      <c r="A41" s="182" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="220"/>
-      <c r="C41" s="220"/>
+      <c r="B41" s="183"/>
+      <c r="C41" s="183"/>
       <c r="D41" s="57" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -4709,27 +4706,27 @@
         <f>AVERAGE(F11:F40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="180" t="e">
+      <c r="G41" s="224" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="181"/>
-      <c r="I41" s="178" t="e">
+      <c r="H41" s="225"/>
+      <c r="I41" s="222" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="179"/>
+      <c r="J41" s="223"/>
       <c r="K41" s="59" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="221" t="s">
+      <c r="A42" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="222"/>
-      <c r="C42" s="222"/>
+      <c r="B42" s="185"/>
+      <c r="C42" s="185"/>
       <c r="D42" s="60">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -4742,27 +4739,27 @@
         <f>MIN(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="186">
+      <c r="G42" s="217">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="187"/>
-      <c r="I42" s="190">
+      <c r="H42" s="218"/>
+      <c r="I42" s="210">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="191"/>
+      <c r="J42" s="211"/>
       <c r="K42" s="62">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="216" t="s">
+      <c r="A43" s="178" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="217"/>
-      <c r="C43" s="217"/>
+      <c r="B43" s="179"/>
+      <c r="C43" s="179"/>
       <c r="D43" s="63">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4775,16 +4772,16 @@
         <f>MAX(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="184">
+      <c r="G43" s="215">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="185"/>
-      <c r="I43" s="182">
+      <c r="H43" s="216"/>
+      <c r="I43" s="212">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="183"/>
+      <c r="J43" s="213"/>
       <c r="K43" s="65">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -4794,8 +4791,8 @@
       <c r="A44" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="151"/>
-      <c r="C44" s="151"/>
+      <c r="B44" s="171"/>
+      <c r="C44" s="171"/>
       <c r="D44" s="38" t="s">
         <v>22</v>
       </c>
@@ -4812,8 +4809,8 @@
     </row>
     <row r="45" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="43"/>
-      <c r="B45" s="150"/>
-      <c r="C45" s="150"/>
+      <c r="B45" s="170"/>
+      <c r="C45" s="170"/>
       <c r="D45" s="38"/>
       <c r="F45" s="39"/>
       <c r="G45" s="40"/>
@@ -4822,15 +4819,15 @@
       <c r="J45" s="17"/>
     </row>
     <row r="46" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
+      <c r="B46" s="155"/>
+      <c r="C46" s="155"/>
       <c r="D46" s="38"/>
       <c r="E46" s="38"/>
       <c r="F46" s="40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G46" s="39">
         <f>Page1!G44</f>
@@ -4839,11 +4836,11 @@
       <c r="H46" s="38"/>
     </row>
     <row r="47" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="133" t="s">
-        <v>131</v>
-      </c>
-      <c r="B47" s="133"/>
-      <c r="C47" s="133"/>
+      <c r="A47" s="155" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="155"/>
+      <c r="C47" s="155"/>
       <c r="D47" s="38"/>
       <c r="E47" s="38"/>
       <c r="F47" s="38"/>
@@ -4898,47 +4895,43 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H10"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
     <mergeCell ref="I43:J43"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G40:H40"/>
@@ -4955,43 +4948,47 @@
     <mergeCell ref="G34:H34"/>
     <mergeCell ref="G35:H35"/>
     <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H10"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
@@ -5047,35 +5044,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
       <c r="K1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
       <c r="K2" s="16" t="s">
         <v>29</v>
       </c>
@@ -5096,15 +5093,15 @@
       <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="153" t="s">
+      <c r="A4" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="209">
+      <c r="B4" s="135"/>
+      <c r="C4" s="205">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="210"/>
+      <c r="D4" s="181"/>
       <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
@@ -5122,22 +5119,22 @@
       <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201">
+      <c r="J4" s="198">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="202"/>
+      <c r="K4" s="199"/>
     </row>
     <row r="5" spans="1:11" s="15" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="159" t="s">
+      <c r="A5" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="160"/>
-      <c r="C5" s="163">
+      <c r="B5" s="143"/>
+      <c r="C5" s="146">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="164"/>
+      <c r="D5" s="147"/>
       <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
@@ -5155,79 +5152,79 @@
       <c r="I5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="203">
+      <c r="J5" s="200">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="204"/>
+      <c r="K5" s="201"/>
     </row>
     <row r="6" spans="1:11" s="15" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="226" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="227"/>
-      <c r="C6" s="228"/>
-      <c r="D6" s="229"/>
-      <c r="E6" s="165"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="158"/>
+      <c r="A6" s="229" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="230"/>
+      <c r="C6" s="231"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="148"/>
+      <c r="G6" s="141"/>
       <c r="H6" s="19"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="196"/>
-      <c r="K6" s="206"/>
+      <c r="I6" s="175"/>
+      <c r="J6" s="176"/>
+      <c r="K6" s="202"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="211" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="196"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="218" t="s">
+      <c r="A7" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="176"/>
+      <c r="C7" s="176"/>
+      <c r="D7" s="180" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="235"/>
-      <c r="F7" s="235"/>
-      <c r="G7" s="210"/>
-      <c r="H7" s="230" t="s">
-        <v>123</v>
-      </c>
-      <c r="I7" s="212"/>
-      <c r="J7" s="198"/>
-      <c r="K7" s="207"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="181"/>
+      <c r="H7" s="233" t="s">
+        <v>122</v>
+      </c>
+      <c r="I7" s="186"/>
+      <c r="J7" s="195"/>
+      <c r="K7" s="203"/>
     </row>
     <row r="8" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="212"/>
-      <c r="B8" s="198"/>
-      <c r="C8" s="198"/>
-      <c r="D8" s="233" t="s">
+      <c r="A8" s="186"/>
+      <c r="B8" s="195"/>
+      <c r="C8" s="195"/>
+      <c r="D8" s="236" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" s="188" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="188" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="224" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" s="224" t="s">
-        <v>142</v>
-      </c>
-      <c r="G8" s="224" t="s">
+      <c r="G8" s="188" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="231"/>
-      <c r="I8" s="212"/>
-      <c r="J8" s="198"/>
-      <c r="K8" s="207"/>
+      <c r="H8" s="234"/>
+      <c r="I8" s="186"/>
+      <c r="J8" s="195"/>
+      <c r="K8" s="203"/>
     </row>
     <row r="9" spans="1:11" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="212"/>
-      <c r="B9" s="198"/>
-      <c r="C9" s="198"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="232"/>
-      <c r="I9" s="212"/>
-      <c r="J9" s="198"/>
-      <c r="K9" s="207"/>
+      <c r="A9" s="186"/>
+      <c r="B9" s="195"/>
+      <c r="C9" s="195"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="186"/>
+      <c r="J9" s="195"/>
+      <c r="K9" s="203"/>
     </row>
     <row r="10" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="86">
@@ -5247,9 +5244,9 @@
       <c r="F10" s="22"/>
       <c r="G10" s="23"/>
       <c r="H10" s="24"/>
-      <c r="I10" s="212"/>
-      <c r="J10" s="198"/>
-      <c r="K10" s="207"/>
+      <c r="I10" s="186"/>
+      <c r="J10" s="195"/>
+      <c r="K10" s="203"/>
     </row>
     <row r="11" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="89">
@@ -5269,9 +5266,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="27"/>
       <c r="H11" s="28"/>
-      <c r="I11" s="212"/>
-      <c r="J11" s="198"/>
-      <c r="K11" s="207"/>
+      <c r="I11" s="186"/>
+      <c r="J11" s="195"/>
+      <c r="K11" s="203"/>
     </row>
     <row r="12" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="89">
@@ -5291,9 +5288,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="27"/>
       <c r="H12" s="28"/>
-      <c r="I12" s="212"/>
-      <c r="J12" s="198"/>
-      <c r="K12" s="207"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="195"/>
+      <c r="K12" s="203"/>
     </row>
     <row r="13" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="89">
@@ -5313,9 +5310,9 @@
       <c r="F13" s="22"/>
       <c r="G13" s="23"/>
       <c r="H13" s="28"/>
-      <c r="I13" s="212"/>
-      <c r="J13" s="198"/>
-      <c r="K13" s="207"/>
+      <c r="I13" s="186"/>
+      <c r="J13" s="195"/>
+      <c r="K13" s="203"/>
     </row>
     <row r="14" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="89">
@@ -5335,9 +5332,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="27"/>
       <c r="H14" s="28"/>
-      <c r="I14" s="212"/>
-      <c r="J14" s="198"/>
-      <c r="K14" s="207"/>
+      <c r="I14" s="186"/>
+      <c r="J14" s="195"/>
+      <c r="K14" s="203"/>
     </row>
     <row r="15" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="89">
@@ -5357,9 +5354,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="27"/>
       <c r="H15" s="28"/>
-      <c r="I15" s="212"/>
-      <c r="J15" s="198"/>
-      <c r="K15" s="207"/>
+      <c r="I15" s="186"/>
+      <c r="J15" s="195"/>
+      <c r="K15" s="203"/>
     </row>
     <row r="16" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="89">
@@ -5379,9 +5376,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="27"/>
       <c r="H16" s="28"/>
-      <c r="I16" s="212"/>
-      <c r="J16" s="198"/>
-      <c r="K16" s="207"/>
+      <c r="I16" s="186"/>
+      <c r="J16" s="195"/>
+      <c r="K16" s="203"/>
     </row>
     <row r="17" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="89">
@@ -5401,9 +5398,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="27"/>
       <c r="H17" s="28"/>
-      <c r="I17" s="212"/>
-      <c r="J17" s="198"/>
-      <c r="K17" s="207"/>
+      <c r="I17" s="186"/>
+      <c r="J17" s="195"/>
+      <c r="K17" s="203"/>
     </row>
     <row r="18" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="89">
@@ -5423,9 +5420,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="27"/>
       <c r="H18" s="28"/>
-      <c r="I18" s="212"/>
-      <c r="J18" s="198"/>
-      <c r="K18" s="207"/>
+      <c r="I18" s="186"/>
+      <c r="J18" s="195"/>
+      <c r="K18" s="203"/>
     </row>
     <row r="19" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="89">
@@ -5445,9 +5442,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="27"/>
       <c r="H19" s="28"/>
-      <c r="I19" s="212"/>
-      <c r="J19" s="198"/>
-      <c r="K19" s="207"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="195"/>
+      <c r="K19" s="203"/>
     </row>
     <row r="20" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="95">
@@ -5467,9 +5464,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="27"/>
       <c r="H20" s="28"/>
-      <c r="I20" s="212"/>
-      <c r="J20" s="198"/>
-      <c r="K20" s="207"/>
+      <c r="I20" s="186"/>
+      <c r="J20" s="195"/>
+      <c r="K20" s="203"/>
     </row>
     <row r="21" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="89">
@@ -5489,9 +5486,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="27"/>
       <c r="H21" s="28"/>
-      <c r="I21" s="212"/>
-      <c r="J21" s="198"/>
-      <c r="K21" s="207"/>
+      <c r="I21" s="186"/>
+      <c r="J21" s="195"/>
+      <c r="K21" s="203"/>
     </row>
     <row r="22" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="89">
@@ -5511,9 +5508,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="27"/>
       <c r="H22" s="28"/>
-      <c r="I22" s="212"/>
-      <c r="J22" s="198"/>
-      <c r="K22" s="207"/>
+      <c r="I22" s="186"/>
+      <c r="J22" s="195"/>
+      <c r="K22" s="203"/>
     </row>
     <row r="23" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="89">
@@ -5533,9 +5530,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
-      <c r="I23" s="212"/>
-      <c r="J23" s="198"/>
-      <c r="K23" s="207"/>
+      <c r="I23" s="186"/>
+      <c r="J23" s="195"/>
+      <c r="K23" s="203"/>
     </row>
     <row r="24" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="89">
@@ -5555,9 +5552,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
-      <c r="I24" s="212"/>
-      <c r="J24" s="198"/>
-      <c r="K24" s="207"/>
+      <c r="I24" s="186"/>
+      <c r="J24" s="195"/>
+      <c r="K24" s="203"/>
     </row>
     <row r="25" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="89">
@@ -5577,9 +5574,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="27"/>
       <c r="H25" s="28"/>
-      <c r="I25" s="212"/>
-      <c r="J25" s="198"/>
-      <c r="K25" s="207"/>
+      <c r="I25" s="186"/>
+      <c r="J25" s="195"/>
+      <c r="K25" s="203"/>
     </row>
     <row r="26" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="89">
@@ -5599,9 +5596,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="27"/>
       <c r="H26" s="28"/>
-      <c r="I26" s="212"/>
-      <c r="J26" s="198"/>
-      <c r="K26" s="207"/>
+      <c r="I26" s="186"/>
+      <c r="J26" s="195"/>
+      <c r="K26" s="203"/>
     </row>
     <row r="27" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="89">
@@ -5621,9 +5618,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28"/>
-      <c r="I27" s="212"/>
-      <c r="J27" s="198"/>
-      <c r="K27" s="207"/>
+      <c r="I27" s="186"/>
+      <c r="J27" s="195"/>
+      <c r="K27" s="203"/>
     </row>
     <row r="28" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="89">
@@ -5643,9 +5640,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="27"/>
       <c r="H28" s="28"/>
-      <c r="I28" s="212"/>
-      <c r="J28" s="198"/>
-      <c r="K28" s="207"/>
+      <c r="I28" s="186"/>
+      <c r="J28" s="195"/>
+      <c r="K28" s="203"/>
     </row>
     <row r="29" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="89">
@@ -5665,9 +5662,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="27"/>
       <c r="H29" s="28"/>
-      <c r="I29" s="212"/>
-      <c r="J29" s="198"/>
-      <c r="K29" s="207"/>
+      <c r="I29" s="186"/>
+      <c r="J29" s="195"/>
+      <c r="K29" s="203"/>
     </row>
     <row r="30" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="95">
@@ -5687,9 +5684,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="27"/>
       <c r="H30" s="28"/>
-      <c r="I30" s="212"/>
-      <c r="J30" s="198"/>
-      <c r="K30" s="207"/>
+      <c r="I30" s="186"/>
+      <c r="J30" s="195"/>
+      <c r="K30" s="203"/>
     </row>
     <row r="31" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="89">
@@ -5709,9 +5706,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="27"/>
       <c r="H31" s="28"/>
-      <c r="I31" s="212"/>
-      <c r="J31" s="198"/>
-      <c r="K31" s="207"/>
+      <c r="I31" s="186"/>
+      <c r="J31" s="195"/>
+      <c r="K31" s="203"/>
     </row>
     <row r="32" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="89">
@@ -5731,9 +5728,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="27"/>
       <c r="H32" s="28"/>
-      <c r="I32" s="212"/>
-      <c r="J32" s="198"/>
-      <c r="K32" s="207"/>
+      <c r="I32" s="186"/>
+      <c r="J32" s="195"/>
+      <c r="K32" s="203"/>
     </row>
     <row r="33" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="89">
@@ -5753,9 +5750,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="27"/>
       <c r="H33" s="28"/>
-      <c r="I33" s="212"/>
-      <c r="J33" s="198"/>
-      <c r="K33" s="207"/>
+      <c r="I33" s="186"/>
+      <c r="J33" s="195"/>
+      <c r="K33" s="203"/>
     </row>
     <row r="34" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="89">
@@ -5775,9 +5772,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="27"/>
       <c r="H34" s="28"/>
-      <c r="I34" s="212"/>
-      <c r="J34" s="198"/>
-      <c r="K34" s="207"/>
+      <c r="I34" s="186"/>
+      <c r="J34" s="195"/>
+      <c r="K34" s="203"/>
     </row>
     <row r="35" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="89">
@@ -5797,9 +5794,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="27"/>
       <c r="H35" s="28"/>
-      <c r="I35" s="212"/>
-      <c r="J35" s="198"/>
-      <c r="K35" s="207"/>
+      <c r="I35" s="186"/>
+      <c r="J35" s="195"/>
+      <c r="K35" s="203"/>
     </row>
     <row r="36" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="89">
@@ -5819,9 +5816,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="27"/>
       <c r="H36" s="28"/>
-      <c r="I36" s="212"/>
-      <c r="J36" s="198"/>
-      <c r="K36" s="207"/>
+      <c r="I36" s="186"/>
+      <c r="J36" s="195"/>
+      <c r="K36" s="203"/>
     </row>
     <row r="37" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="89">
@@ -5841,9 +5838,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="27"/>
       <c r="H37" s="28"/>
-      <c r="I37" s="212"/>
-      <c r="J37" s="198"/>
-      <c r="K37" s="207"/>
+      <c r="I37" s="186"/>
+      <c r="J37" s="195"/>
+      <c r="K37" s="203"/>
     </row>
     <row r="38" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="89">
@@ -5863,9 +5860,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="27"/>
       <c r="H38" s="28"/>
-      <c r="I38" s="212"/>
-      <c r="J38" s="198"/>
-      <c r="K38" s="207"/>
+      <c r="I38" s="186"/>
+      <c r="J38" s="195"/>
+      <c r="K38" s="203"/>
     </row>
     <row r="39" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="96">
@@ -5885,16 +5882,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="27"/>
       <c r="H39" s="28"/>
-      <c r="I39" s="212"/>
-      <c r="J39" s="198"/>
-      <c r="K39" s="207"/>
+      <c r="I39" s="186"/>
+      <c r="J39" s="195"/>
+      <c r="K39" s="203"/>
     </row>
     <row r="40" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="236" t="s">
+      <c r="A40" s="227" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="237"/>
-      <c r="C40" s="237"/>
+      <c r="B40" s="228"/>
+      <c r="C40" s="228"/>
       <c r="D40" s="29" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -5915,16 +5912,16 @@
         <f>AVERAGE(H10:H39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="198"/>
-      <c r="J40" s="198"/>
-      <c r="K40" s="207"/>
+      <c r="I40" s="195"/>
+      <c r="J40" s="195"/>
+      <c r="K40" s="203"/>
     </row>
     <row r="41" spans="1:11" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="221" t="s">
+      <c r="A41" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="222"/>
-      <c r="C41" s="222"/>
+      <c r="B41" s="185"/>
+      <c r="C41" s="185"/>
       <c r="D41" s="32">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -5945,16 +5942,16 @@
         <f>MIN(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="198"/>
-      <c r="J41" s="198"/>
-      <c r="K41" s="207"/>
+      <c r="I41" s="195"/>
+      <c r="J41" s="195"/>
+      <c r="K41" s="203"/>
     </row>
     <row r="42" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="216" t="s">
+      <c r="A42" s="178" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="217"/>
-      <c r="C42" s="217"/>
+      <c r="B42" s="179"/>
+      <c r="C42" s="179"/>
       <c r="D42" s="35">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -5975,16 +5972,16 @@
         <f>MAX(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="200"/>
-      <c r="J42" s="200"/>
-      <c r="K42" s="208"/>
+      <c r="I42" s="197"/>
+      <c r="J42" s="197"/>
+      <c r="K42" s="204"/>
     </row>
     <row r="43" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="151"/>
-      <c r="C43" s="151"/>
+      <c r="B43" s="171"/>
+      <c r="C43" s="171"/>
       <c r="D43" s="38" t="s">
         <v>22</v>
       </c>
@@ -6001,8 +5998,8 @@
     </row>
     <row r="44" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="43"/>
-      <c r="B44" s="150"/>
-      <c r="C44" s="150"/>
+      <c r="B44" s="170"/>
+      <c r="C44" s="170"/>
       <c r="D44" s="38"/>
       <c r="F44" s="39"/>
       <c r="G44" s="40"/>
@@ -6011,15 +6008,15 @@
       <c r="J44" s="17"/>
     </row>
     <row r="45" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="133" t="s">
+      <c r="A45" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
+      <c r="B45" s="155"/>
+      <c r="C45" s="155"/>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
       <c r="F45" s="40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G45" s="39">
         <f>Page1!G44</f>
@@ -6028,11 +6025,11 @@
       <c r="H45" s="38"/>
     </row>
     <row r="46" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="133" t="s">
-        <v>131</v>
-      </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
+      <c r="A46" s="155" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" s="155"/>
+      <c r="C46" s="155"/>
       <c r="D46" s="38"/>
       <c r="E46" s="38"/>
       <c r="F46" s="38"/>
@@ -6057,15 +6054,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:C9"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="A1:J1"/>
@@ -6082,6 +6070,15 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A7:C9"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="notBetween">
@@ -6128,15 +6125,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="242" t="s">
+      <c r="A1" s="304" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="243"/>
-      <c r="C1" s="243"/>
-      <c r="D1" s="243"/>
-      <c r="E1" s="243"/>
-      <c r="F1" s="243"/>
-      <c r="G1" s="244"/>
+      <c r="B1" s="305"/>
+      <c r="C1" s="305"/>
+      <c r="D1" s="305"/>
+      <c r="E1" s="305"/>
+      <c r="F1" s="305"/>
+      <c r="G1" s="306"/>
     </row>
     <row r="2" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="100"/>
@@ -6150,37 +6147,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="287" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="288"/>
-      <c r="C3" s="288"/>
-      <c r="D3" s="288"/>
-      <c r="E3" s="288"/>
-      <c r="F3" s="288"/>
-      <c r="G3" s="289"/>
+      <c r="A3" s="242" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="243"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="212" t="s">
+      <c r="A4" s="186" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="198"/>
-      <c r="C4" s="198"/>
-      <c r="D4" s="198"/>
-      <c r="E4" s="198"/>
-      <c r="F4" s="198"/>
-      <c r="G4" s="207"/>
+      <c r="B4" s="195"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="203"/>
     </row>
     <row r="5" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="284" t="s">
+      <c r="A5" s="239" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="285"/>
-      <c r="C5" s="285"/>
-      <c r="D5" s="285"/>
-      <c r="E5" s="285"/>
-      <c r="F5" s="285"/>
-      <c r="G5" s="286"/>
+      <c r="B5" s="240"/>
+      <c r="C5" s="240"/>
+      <c r="D5" s="240"/>
+      <c r="E5" s="240"/>
+      <c r="F5" s="240"/>
+      <c r="G5" s="241"/>
     </row>
     <row r="6" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103" t="s">
@@ -6192,12 +6189,13 @@
       <c r="C6" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="245" t="s">
+      <c r="D6" s="269">
+        <f>Page1!H4</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="271"/>
+      <c r="F6" s="302" t="s">
         <v>49</v>
-      </c>
-      <c r="E6" s="246"/>
-      <c r="F6" s="238" t="s">
-        <v>50</v>
       </c>
       <c r="G6" s="247">
         <f>Page1!J4</f>
@@ -6206,37 +6204,37 @@
     </row>
     <row r="7" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="107"/>
       <c r="C7" s="105" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="245">
+        <v>51</v>
+      </c>
+      <c r="D7" s="269">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="246"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="248"/>
+      <c r="E7" s="271"/>
+      <c r="F7" s="302"/>
+      <c r="G7" s="307"/>
     </row>
     <row r="8" spans="1:7" s="99" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="103" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="106">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
       <c r="C8" s="105" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="238">
+        <v>53</v>
+      </c>
+      <c r="D8" s="302">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="238"/>
-      <c r="F8" s="239" t="s">
+      <c r="E8" s="302"/>
+      <c r="F8" s="250" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="247">
@@ -6246,76 +6244,76 @@
     </row>
     <row r="9" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="109" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9" s="108">
         <f>Page1!G44</f>
         <v>461303600</v>
       </c>
-      <c r="C9" s="239" t="s">
+      <c r="C9" s="250" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="252" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="294" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="295"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="292"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="303"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="1:7" s="99" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="110" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="111">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="241"/>
-      <c r="D10" s="296"/>
-      <c r="E10" s="297"/>
-      <c r="F10" s="241"/>
-      <c r="G10" s="293"/>
+      <c r="C10" s="251"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="255"/>
+      <c r="F10" s="251"/>
+      <c r="G10" s="249"/>
     </row>
     <row r="11" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="298" t="s">
+      <c r="A11" s="256" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="258" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="300" t="s">
+      <c r="C11" s="260" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="261"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="258" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="302" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="303"/>
-      <c r="E11" s="304"/>
-      <c r="F11" s="300" t="s">
+      <c r="G11" s="263" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="305" t="s">
+    </row>
+    <row r="12" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="257"/>
+      <c r="B12" s="259"/>
+      <c r="C12" s="112" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="299"/>
-      <c r="B12" s="301"/>
-      <c r="C12" s="112" t="s">
+      <c r="D12" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="112" t="s">
+      <c r="E12" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="112" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="301"/>
-      <c r="G12" s="306"/>
+      <c r="F12" s="259"/>
+      <c r="G12" s="264"/>
     </row>
     <row r="13" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="113" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="114" t="s">
         <v>66</v>
-      </c>
-      <c r="B13" s="114" t="s">
-        <v>67</v>
       </c>
       <c r="C13" s="115">
         <v>17</v>
@@ -6331,15 +6329,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G13" s="82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="117" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="118" t="s">
         <v>69</v>
-      </c>
-      <c r="B14" s="118" t="s">
-        <v>70</v>
       </c>
       <c r="C14" s="119">
         <v>18</v>
@@ -6355,15 +6353,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G14" s="121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="117" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="118" t="s">
         <v>72</v>
-      </c>
-      <c r="B15" s="118" t="s">
-        <v>73</v>
       </c>
       <c r="C15" s="119">
         <v>300</v>
@@ -6378,16 +6376,16 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="249" t="s">
-        <v>74</v>
+      <c r="G15" s="298" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="117" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" s="118" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="119">
         <v>300</v>
@@ -6402,14 +6400,14 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="231"/>
+      <c r="G16" s="234"/>
     </row>
     <row r="17" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="117" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="118" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="119">
         <v>900</v>
@@ -6424,14 +6422,14 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="231"/>
+      <c r="G17" s="234"/>
     </row>
     <row r="18" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="117" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" s="118" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="119">
         <v>700</v>
@@ -6446,14 +6444,14 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="231"/>
+      <c r="G18" s="234"/>
     </row>
     <row r="19" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="117" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="118" t="s">
         <v>78</v>
-      </c>
-      <c r="B19" s="118" t="s">
-        <v>79</v>
       </c>
       <c r="C19" s="119">
         <v>350</v>
@@ -6468,14 +6466,14 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="231"/>
+      <c r="G19" s="234"/>
     </row>
     <row r="20" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="117" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" s="118" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" s="119">
         <v>400</v>
@@ -6490,11 +6488,11 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="231"/>
+      <c r="G20" s="234"/>
     </row>
     <row r="21" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="117" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="118" t="s">
         <v>40</v>
@@ -6512,11 +6510,11 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="231"/>
+      <c r="G21" s="234"/>
     </row>
     <row r="22" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="117" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" s="118" t="s">
         <v>40</v>
@@ -6534,14 +6532,14 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="167"/>
+      <c r="G22" s="150"/>
     </row>
     <row r="23" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="117" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="118" t="s">
         <v>83</v>
-      </c>
-      <c r="B23" s="118" t="s">
-        <v>84</v>
       </c>
       <c r="C23" s="61">
         <v>360</v>
@@ -6557,15 +6555,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G23" s="121" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="117" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="118" t="s">
         <v>86</v>
-      </c>
-      <c r="B24" s="118" t="s">
-        <v>87</v>
       </c>
       <c r="C24" s="119" t="s">
         <v>40</v>
@@ -6583,15 +6581,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G24" s="121" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="117" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="118" t="s">
         <v>89</v>
-      </c>
-      <c r="B25" s="118" t="s">
-        <v>90</v>
       </c>
       <c r="C25" s="61">
         <v>6000</v>
@@ -6606,15 +6604,15 @@
         <v>6000</v>
       </c>
       <c r="G25" s="121" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="123" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B26" s="124" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C26" s="83">
         <v>410</v>
@@ -6630,289 +6628,328 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G26" s="122" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="250" t="s">
+      <c r="A27" s="295" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="296"/>
+      <c r="C27" s="296"/>
+      <c r="D27" s="296"/>
+      <c r="E27" s="296"/>
+      <c r="F27" s="296"/>
+      <c r="G27" s="297"/>
+    </row>
+    <row r="28" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="267" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="251"/>
-      <c r="C27" s="251"/>
-      <c r="D27" s="251"/>
-      <c r="E27" s="251"/>
-      <c r="F27" s="251"/>
-      <c r="G27" s="252"/>
-    </row>
-    <row r="28" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="253" t="s">
+      <c r="B28" s="268"/>
+      <c r="C28" s="299" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="254"/>
-      <c r="C28" s="255" t="s">
+      <c r="D28" s="300"/>
+      <c r="E28" s="301"/>
+      <c r="F28" s="126" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="256"/>
-      <c r="E28" s="257"/>
-      <c r="F28" s="126" t="s">
+      <c r="G28" s="82" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="272" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="271"/>
+      <c r="C29" s="289" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="290"/>
+      <c r="E29" s="291"/>
+      <c r="F29" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="121" t="s">
         <v>96</v>
       </c>
-      <c r="G28" s="82" t="s">
+    </row>
+    <row r="30" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="272" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="271"/>
+      <c r="C30" s="289" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="290"/>
+      <c r="E30" s="291"/>
+      <c r="F30" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="82" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="272" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" s="271"/>
+      <c r="C31" s="289" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" s="290"/>
+      <c r="E31" s="291"/>
+      <c r="F31" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="121" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="272" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="271"/>
+      <c r="C32" s="289" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="290"/>
+      <c r="E32" s="291"/>
+      <c r="F32" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32" s="121" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="272" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="271"/>
+      <c r="C33" s="289" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="290"/>
+      <c r="E33" s="291"/>
+      <c r="F33" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="G33" s="121" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="258" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" s="246"/>
-      <c r="C29" s="259" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" s="260"/>
-      <c r="E29" s="261"/>
-      <c r="F29" s="60" t="s">
+    <row r="34" spans="1:7" s="99" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="142" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="143"/>
+      <c r="C34" s="292" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="293"/>
+      <c r="E34" s="294"/>
+      <c r="F34" s="127" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34" s="132" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="295" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="296"/>
+      <c r="C35" s="296"/>
+      <c r="D35" s="296"/>
+      <c r="E35" s="296"/>
+      <c r="F35" s="296"/>
+      <c r="G35" s="297"/>
+    </row>
+    <row r="36" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="134" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="135"/>
+      <c r="C36" s="287" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="288"/>
+      <c r="E36" s="135"/>
+      <c r="F36" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G36" s="82" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="267" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="268"/>
+      <c r="C37" s="269" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="270"/>
+      <c r="E37" s="271"/>
+      <c r="F37" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="G37" s="121" t="s">
         <v>96</v>
       </c>
-      <c r="G29" s="121" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="258" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="246"/>
-      <c r="C30" s="259" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="260"/>
-      <c r="E30" s="261"/>
-      <c r="F30" s="60" t="s">
+    </row>
+    <row r="38" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="272" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" s="271"/>
+      <c r="C38" s="269" t="s">
+        <v>115</v>
+      </c>
+      <c r="D38" s="270"/>
+      <c r="E38" s="271"/>
+      <c r="F38" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="G38" s="121" t="s">
         <v>96</v>
       </c>
-      <c r="G30" s="82" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="258" t="s">
-        <v>102</v>
-      </c>
-      <c r="B31" s="246"/>
-      <c r="C31" s="259" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" s="260"/>
-      <c r="E31" s="261"/>
-      <c r="F31" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" s="121" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="258" t="s">
-        <v>105</v>
-      </c>
-      <c r="B32" s="246"/>
-      <c r="C32" s="259" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" s="260"/>
-      <c r="E32" s="261"/>
-      <c r="F32" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G32" s="121" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="258" t="s">
-        <v>107</v>
-      </c>
-      <c r="B33" s="246"/>
-      <c r="C33" s="259" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" s="260"/>
-      <c r="E33" s="261"/>
-      <c r="F33" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G33" s="121" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="99" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="159" t="s">
-        <v>109</v>
-      </c>
-      <c r="B34" s="160"/>
-      <c r="C34" s="264" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" s="265"/>
-      <c r="E34" s="266"/>
-      <c r="F34" s="127" t="s">
-        <v>96</v>
-      </c>
-      <c r="G34" s="132" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="250" t="s">
-        <v>111</v>
-      </c>
-      <c r="B35" s="251"/>
-      <c r="C35" s="251"/>
-      <c r="D35" s="251"/>
-      <c r="E35" s="251"/>
-      <c r="F35" s="251"/>
-      <c r="G35" s="252"/>
-    </row>
-    <row r="36" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="153" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="154"/>
-      <c r="C36" s="262" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" s="263"/>
-      <c r="E36" s="154"/>
-      <c r="F36" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G36" s="82" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="253" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="254"/>
-      <c r="C37" s="245" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" s="268"/>
-      <c r="E37" s="246"/>
-      <c r="F37" s="119" t="s">
-        <v>96</v>
-      </c>
-      <c r="G37" s="121" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="258" t="s">
-        <v>115</v>
-      </c>
-      <c r="B38" s="246"/>
-      <c r="C38" s="245" t="s">
+    </row>
+    <row r="39" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="142" t="s">
         <v>116</v>
       </c>
-      <c r="D38" s="268"/>
-      <c r="E38" s="246"/>
-      <c r="F38" s="119" t="s">
-        <v>96</v>
-      </c>
-      <c r="G38" s="121" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="159" t="s">
+      <c r="B39" s="143"/>
+      <c r="C39" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="160"/>
-      <c r="C39" s="290" t="s">
+      <c r="D39" s="246"/>
+      <c r="E39" s="143"/>
+      <c r="F39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G39" s="122" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="273" t="s">
         <v>118</v>
       </c>
-      <c r="D39" s="291"/>
-      <c r="E39" s="160"/>
-      <c r="F39" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G39" s="122" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="269" t="s">
-        <v>119</v>
-      </c>
-      <c r="B40" s="270"/>
-      <c r="C40" s="271" t="s">
+      <c r="B40" s="274"/>
+      <c r="C40" s="275" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" s="276"/>
+      <c r="E40" s="277"/>
+      <c r="F40" s="275" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="272"/>
-      <c r="E40" s="273"/>
-      <c r="F40" s="271" t="s">
+      <c r="G40" s="277"/>
+    </row>
+    <row r="41" spans="1:7" s="99" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="278"/>
+      <c r="B41" s="279"/>
+      <c r="C41" s="186"/>
+      <c r="D41" s="195"/>
+      <c r="E41" s="203"/>
+      <c r="F41" s="282"/>
+      <c r="G41" s="283"/>
+    </row>
+    <row r="42" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="280"/>
+      <c r="B42" s="281"/>
+      <c r="C42" s="284" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="285"/>
+      <c r="E42" s="286"/>
+      <c r="F42" s="284" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="273"/>
-    </row>
-    <row r="41" spans="1:7" s="99" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="274"/>
-      <c r="B41" s="275"/>
-      <c r="C41" s="212"/>
-      <c r="D41" s="198"/>
-      <c r="E41" s="207"/>
-      <c r="F41" s="278"/>
-      <c r="G41" s="279"/>
-    </row>
-    <row r="42" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="276"/>
-      <c r="B42" s="277"/>
-      <c r="C42" s="280" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="281"/>
-      <c r="E42" s="282"/>
-      <c r="F42" s="280" t="s">
-        <v>139</v>
-      </c>
-      <c r="G42" s="282"/>
+      <c r="G42" s="286"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="128"/>
       <c r="B43" s="128"/>
       <c r="C43" s="128"/>
       <c r="D43" s="128"/>
-      <c r="E43" s="307"/>
-      <c r="F43" s="307"/>
-      <c r="G43" s="307"/>
+      <c r="E43" s="265"/>
+      <c r="F43" s="265"/>
+      <c r="G43" s="265"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B44" s="129"/>
       <c r="C44" s="131"/>
       <c r="D44" s="128"/>
-      <c r="E44" s="267"/>
-      <c r="F44" s="267"/>
-      <c r="G44" s="267"/>
+      <c r="E44" s="266"/>
+      <c r="F44" s="266"/>
+      <c r="G44" s="266"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="283" t="s">
+      <c r="A46" s="238" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="238"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="238" t="s">
         <v>121</v>
       </c>
-      <c r="B46" s="283"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="283" t="s">
-        <v>122</v>
-      </c>
-      <c r="B47" s="283"/>
+      <c r="B47" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="G15:G22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="A41:B42"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:G42"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A4:G4"/>
@@ -6929,45 +6966,6 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="G15:G22"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.78740157480314965" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/UC-18gsm-250P-ABQR.xlsx
+++ b/backend/templates/UC-18gsm-250P-ABQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31E0DFD-7725-4E2F-BBC0-22D55FE6D563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E4CC3E-540B-44B6-BF22-CB0F7EE51F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1443,7 +1443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2329,21 +2329,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2406,6 +2391,24 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6125,15 +6128,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="304" t="s">
+      <c r="A1" s="299" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="305"/>
-      <c r="C1" s="305"/>
-      <c r="D1" s="305"/>
-      <c r="E1" s="305"/>
-      <c r="F1" s="305"/>
-      <c r="G1" s="306"/>
+      <c r="B1" s="300"/>
+      <c r="C1" s="300"/>
+      <c r="D1" s="300"/>
+      <c r="E1" s="300"/>
+      <c r="F1" s="300"/>
+      <c r="G1" s="301"/>
     </row>
     <row r="2" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="100"/>
@@ -6194,7 +6197,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="271"/>
-      <c r="F6" s="302" t="s">
+      <c r="F6" s="297" t="s">
         <v>49</v>
       </c>
       <c r="G6" s="247">
@@ -6215,8 +6218,8 @@
         <v>0</v>
       </c>
       <c r="E7" s="271"/>
-      <c r="F7" s="302"/>
-      <c r="G7" s="307"/>
+      <c r="F7" s="297"/>
+      <c r="G7" s="302"/>
     </row>
     <row r="8" spans="1:7" s="99" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="103" t="s">
@@ -6229,11 +6232,11 @@
       <c r="C8" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="302">
+      <c r="D8" s="297">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="302"/>
+      <c r="E8" s="297"/>
       <c r="F8" s="250" t="s">
         <v>9</v>
       </c>
@@ -6257,7 +6260,7 @@
         <v>56</v>
       </c>
       <c r="E9" s="253"/>
-      <c r="F9" s="303"/>
+      <c r="F9" s="298"/>
       <c r="G9" s="248"/>
     </row>
     <row r="10" spans="1:7" s="99" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6376,7 +6379,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="298" t="s">
+      <c r="G15" s="293" t="s">
         <v>73</v>
       </c>
     </row>
@@ -6632,26 +6635,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="295" t="s">
+      <c r="A27" s="290" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="296"/>
-      <c r="C27" s="296"/>
-      <c r="D27" s="296"/>
-      <c r="E27" s="296"/>
-      <c r="F27" s="296"/>
-      <c r="G27" s="297"/>
+      <c r="B27" s="291"/>
+      <c r="C27" s="291"/>
+      <c r="D27" s="291"/>
+      <c r="E27" s="291"/>
+      <c r="F27" s="291"/>
+      <c r="G27" s="292"/>
     </row>
     <row r="28" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="267" t="s">
         <v>93</v>
       </c>
       <c r="B28" s="268"/>
-      <c r="C28" s="299" t="s">
+      <c r="C28" s="294" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="300"/>
-      <c r="E28" s="301"/>
+      <c r="D28" s="295"/>
+      <c r="E28" s="296"/>
       <c r="F28" s="126" t="s">
         <v>95</v>
       </c>
@@ -6664,11 +6667,11 @@
         <v>97</v>
       </c>
       <c r="B29" s="271"/>
-      <c r="C29" s="289" t="s">
+      <c r="C29" s="284" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="290"/>
-      <c r="E29" s="291"/>
+      <c r="D29" s="285"/>
+      <c r="E29" s="286"/>
       <c r="F29" s="60" t="s">
         <v>95</v>
       </c>
@@ -6681,11 +6684,11 @@
         <v>99</v>
       </c>
       <c r="B30" s="271"/>
-      <c r="C30" s="289" t="s">
+      <c r="C30" s="284" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="290"/>
-      <c r="E30" s="291"/>
+      <c r="D30" s="285"/>
+      <c r="E30" s="286"/>
       <c r="F30" s="60" t="s">
         <v>95</v>
       </c>
@@ -6698,11 +6701,11 @@
         <v>101</v>
       </c>
       <c r="B31" s="271"/>
-      <c r="C31" s="289" t="s">
+      <c r="C31" s="284" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="290"/>
-      <c r="E31" s="291"/>
+      <c r="D31" s="285"/>
+      <c r="E31" s="286"/>
       <c r="F31" s="60" t="s">
         <v>95</v>
       </c>
@@ -6715,11 +6718,11 @@
         <v>104</v>
       </c>
       <c r="B32" s="271"/>
-      <c r="C32" s="289" t="s">
+      <c r="C32" s="284" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="290"/>
-      <c r="E32" s="291"/>
+      <c r="D32" s="285"/>
+      <c r="E32" s="286"/>
       <c r="F32" s="60" t="s">
         <v>95</v>
       </c>
@@ -6732,11 +6735,11 @@
         <v>106</v>
       </c>
       <c r="B33" s="271"/>
-      <c r="C33" s="289" t="s">
+      <c r="C33" s="284" t="s">
         <v>107</v>
       </c>
-      <c r="D33" s="290"/>
-      <c r="E33" s="291"/>
+      <c r="D33" s="285"/>
+      <c r="E33" s="286"/>
       <c r="F33" s="60" t="s">
         <v>95</v>
       </c>
@@ -6749,11 +6752,11 @@
         <v>108</v>
       </c>
       <c r="B34" s="143"/>
-      <c r="C34" s="292" t="s">
+      <c r="C34" s="287" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="293"/>
-      <c r="E34" s="294"/>
+      <c r="D34" s="288"/>
+      <c r="E34" s="289"/>
       <c r="F34" s="127" t="s">
         <v>95</v>
       </c>
@@ -6762,25 +6765,25 @@
       </c>
     </row>
     <row r="35" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="295" t="s">
+      <c r="A35" s="290" t="s">
         <v>110</v>
       </c>
-      <c r="B35" s="296"/>
-      <c r="C35" s="296"/>
-      <c r="D35" s="296"/>
-      <c r="E35" s="296"/>
-      <c r="F35" s="296"/>
-      <c r="G35" s="297"/>
+      <c r="B35" s="291"/>
+      <c r="C35" s="291"/>
+      <c r="D35" s="291"/>
+      <c r="E35" s="291"/>
+      <c r="F35" s="291"/>
+      <c r="G35" s="292"/>
     </row>
     <row r="36" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="134" t="s">
         <v>111</v>
       </c>
       <c r="B36" s="135"/>
-      <c r="C36" s="287" t="s">
+      <c r="C36" s="282" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="288"/>
+      <c r="D36" s="283"/>
       <c r="E36" s="135"/>
       <c r="F36" s="10" t="s">
         <v>95</v>
@@ -6855,27 +6858,27 @@
       </c>
       <c r="G40" s="277"/>
     </row>
-    <row r="41" spans="1:7" s="99" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" s="99" customFormat="1" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="278"/>
       <c r="B41" s="279"/>
-      <c r="C41" s="186"/>
-      <c r="D41" s="195"/>
-      <c r="E41" s="203"/>
-      <c r="F41" s="282"/>
-      <c r="G41" s="283"/>
-    </row>
-    <row r="42" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="303"/>
+      <c r="D41" s="304"/>
+      <c r="E41" s="305"/>
+      <c r="F41" s="303"/>
+      <c r="G41" s="305"/>
+    </row>
+    <row r="42" spans="1:7" s="99" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="280"/>
       <c r="B42" s="281"/>
-      <c r="C42" s="284" t="s">
+      <c r="C42" s="306" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="285"/>
-      <c r="E42" s="286"/>
-      <c r="F42" s="284" t="s">
+      <c r="D42" s="307"/>
+      <c r="E42" s="308"/>
+      <c r="F42" s="306" t="s">
         <v>138</v>
       </c>
-      <c r="G42" s="286"/>
+      <c r="G42" s="308"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="128"/>
